--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CB4A05-E7F7-4D7B-BF8C-5510838F9678}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5116A1C2-4DA2-4E34-B410-3F0F4880F2EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -38,8 +38,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{A1927ADD-B4F0-4A33-A2A7-A7CC0808A94B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+S.I NO 11198
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -154,7 +190,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,6 +289,19 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -781,7 +830,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392DCC38-B676-43F3-B392-E571D3EDC2BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{392DCC38-B676-43F3-B392-E571D3EDC2BC}">
   <dimension ref="A1:V279"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -1062,15 +1111,27 @@
       <c r="B11" s="27">
         <v>46205</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
+      <c r="C11" s="32">
+        <v>298036</v>
+      </c>
+      <c r="D11" s="32">
+        <v>206</v>
+      </c>
       <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
+      <c r="F11" s="32">
+        <v>1185.43</v>
+      </c>
       <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="31"/>
+      <c r="H11" s="32">
+        <v>206862</v>
+      </c>
+      <c r="I11" s="31">
+        <v>43785</v>
+      </c>
       <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="K11" s="32">
+        <v>127.68</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1958,11 +2019,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>0</v>
+        <v>298036</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -1970,7 +2031,7 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1185.43</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
@@ -1978,11 +2039,11 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>206862</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>0</v>
+        <v>43785</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -1990,7 +2051,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>0</v>
+        <v>127.68</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -5999,6 +6060,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -6292,15 +6354,17 @@
       <c r="B11" s="27">
         <v>46205</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="C11" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="44"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="45"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -11219,7 +11283,8 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="C11:K11"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C28:K28"/>
@@ -11521,12 +11586,22 @@
       <c r="B11" s="27">
         <v>46205</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
+      <c r="C11" s="32">
+        <v>253346.5</v>
+      </c>
+      <c r="D11" s="32">
+        <v>213164</v>
+      </c>
       <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32"/>
+      <c r="F11" s="32">
+        <v>47</v>
+      </c>
+      <c r="G11" s="31">
+        <v>1722</v>
+      </c>
+      <c r="H11" s="32">
+        <v>213211</v>
+      </c>
       <c r="I11" s="31"/>
       <c r="J11" s="32"/>
       <c r="K11" s="32"/>
@@ -12417,11 +12492,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>297996.5</v>
+        <v>551343</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>238892</v>
+        <v>452056</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12429,15 +12504,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>1350</v>
+        <v>3072</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>238871</v>
+        <v>452082</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5116A1C2-4DA2-4E34-B410-3F0F4880F2EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448E8B17-1E3A-410C-BC85-1683013A3939}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1151,12 +1151,22 @@
       <c r="B12" s="27">
         <v>46206</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="31"/>
+      <c r="C12" s="32">
+        <v>331281.5</v>
+      </c>
+      <c r="D12" s="32">
+        <v>274671.5</v>
+      </c>
+      <c r="E12" s="31">
+        <v>1788.5</v>
+      </c>
       <c r="F12" s="32"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="32"/>
+      <c r="G12" s="31">
+        <v>2040</v>
+      </c>
+      <c r="H12" s="32">
+        <v>272883</v>
+      </c>
       <c r="I12" s="31"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
@@ -1179,15 +1189,17 @@
       <c r="B13" s="27">
         <v>46207</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="C13" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -2019,15 +2031,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>298036</v>
+        <v>629317.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>206</v>
+        <v>274877.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1788.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2035,11 +2047,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2040</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>206862</v>
+        <v>479745</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6050,13 +6062,14 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C10:K10"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C35:K35"/>
+    <mergeCell ref="C13:K13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6384,12 +6397,22 @@
       <c r="B12" s="27">
         <v>46206</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
+      <c r="C12" s="32">
+        <v>272174.5</v>
+      </c>
+      <c r="D12" s="32">
+        <v>231067</v>
+      </c>
       <c r="E12" s="31"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="32"/>
+      <c r="F12" s="32">
+        <v>517</v>
+      </c>
+      <c r="G12" s="31">
+        <v>1308</v>
+      </c>
+      <c r="H12" s="32">
+        <v>231584</v>
+      </c>
       <c r="I12" s="31"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
@@ -6412,15 +6435,17 @@
       <c r="B13" s="27">
         <v>46207</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="C13" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -7252,11 +7277,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>249800.5</v>
+        <v>521975</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>211385.5</v>
+        <v>442452.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7264,15 +7289,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>517</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>1644</v>
+        <v>2952</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>210612</v>
+        <v>442196</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11283,13 +11308,14 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="C42:K42"/>
+    <mergeCell ref="C13:K13"/>
     <mergeCell ref="C11:K11"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C35:K35"/>
-    <mergeCell ref="C42:K42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -11624,12 +11650,22 @@
       <c r="B12" s="27">
         <v>46206</v>
       </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
+      <c r="C12" s="32">
+        <v>438059</v>
+      </c>
+      <c r="D12" s="32">
+        <v>402146.75</v>
+      </c>
       <c r="E12" s="31"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="32"/>
+      <c r="F12" s="32">
+        <v>67.25</v>
+      </c>
+      <c r="G12" s="31">
+        <v>648</v>
+      </c>
+      <c r="H12" s="32">
+        <v>402214</v>
+      </c>
       <c r="I12" s="31"/>
       <c r="J12" s="32"/>
       <c r="K12" s="32"/>
@@ -11652,15 +11688,17 @@
       <c r="B13" s="27">
         <v>46207</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="C13" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="45"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -12492,11 +12530,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>551343</v>
+        <v>989402</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>452056</v>
+        <v>854202.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12504,15 +12542,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>114.25</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>3072</v>
+        <v>3720</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>452082</v>
+        <v>854296</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -16523,7 +16561,8 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="C13:K13"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C28:K28"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448E8B17-1E3A-410C-BC85-1683013A3939}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA651E7-8672-4F7E-B840-2B7EB7675253}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1249,12 +1249,22 @@
       <c r="B15" s="27">
         <v>46209</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
+      <c r="C15" s="34">
+        <v>233857</v>
+      </c>
+      <c r="D15" s="34">
+        <v>195673</v>
+      </c>
       <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
+      <c r="F15" s="34">
+        <v>1696</v>
+      </c>
+      <c r="G15" s="31">
+        <v>1326</v>
+      </c>
+      <c r="H15" s="34">
+        <v>197369</v>
+      </c>
       <c r="I15" s="31"/>
       <c r="J15" s="34"/>
       <c r="K15" s="32"/>
@@ -2031,11 +2041,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>629317.5</v>
+        <v>863174.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>274877.5</v>
+        <v>470550.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -2043,15 +2053,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>1185.43</v>
+        <v>2881.4300000000003</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>2040</v>
+        <v>3366</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>479745</v>
+        <v>677114</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6495,12 +6505,22 @@
       <c r="B15" s="27">
         <v>46209</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
+      <c r="C15" s="34">
+        <v>255013.5</v>
+      </c>
+      <c r="D15" s="34">
+        <v>211456.5</v>
+      </c>
+      <c r="E15" s="31">
+        <v>765.5</v>
+      </c>
       <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
+      <c r="G15" s="31">
+        <v>1950</v>
+      </c>
+      <c r="H15" s="34">
+        <v>210691</v>
+      </c>
       <c r="I15" s="31"/>
       <c r="J15" s="34"/>
       <c r="K15" s="32"/>
@@ -7277,15 +7297,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>521975</v>
+        <v>776988.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>442452.5</v>
+        <v>653909</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>773.5</v>
+        <v>1539</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7293,11 +7313,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>2952</v>
+        <v>4902</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>442196</v>
+        <v>652887</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11748,12 +11768,22 @@
       <c r="B15" s="27">
         <v>46209</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
+      <c r="C15" s="34">
+        <v>299824</v>
+      </c>
+      <c r="D15" s="34">
+        <v>247763.5</v>
+      </c>
+      <c r="E15" s="31">
+        <v>34.5</v>
+      </c>
       <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
+      <c r="G15" s="31">
+        <v>2328</v>
+      </c>
+      <c r="H15" s="34">
+        <v>247729</v>
+      </c>
       <c r="I15" s="31"/>
       <c r="J15" s="34"/>
       <c r="K15" s="32"/>
@@ -12530,15 +12560,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>989402</v>
+        <v>1289226</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>854202.75</v>
+        <v>1101966.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>55.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12546,11 +12576,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>3720</v>
+        <v>6048</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>854296</v>
+        <v>1102025</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -16562,12 +16592,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="C42:K42"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C35:K35"/>
-    <mergeCell ref="C42:K42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA651E7-8672-4F7E-B840-2B7EB7675253}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE04124-5088-4D53-ABC2-6EA73AB41444}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -1287,12 +1287,22 @@
       <c r="B16" s="27">
         <v>46210</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
+      <c r="C16" s="34">
+        <v>258311</v>
+      </c>
+      <c r="D16" s="34">
+        <v>218333</v>
+      </c>
+      <c r="E16" s="31">
+        <v>81</v>
+      </c>
       <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
+      <c r="G16" s="31">
+        <v>2010</v>
+      </c>
+      <c r="H16" s="34">
+        <v>218252</v>
+      </c>
       <c r="I16" s="31"/>
       <c r="J16" s="34"/>
       <c r="K16" s="32"/>
@@ -2041,15 +2051,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>863174.5</v>
+        <v>1121485.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>470550.5</v>
+        <v>688883.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>1788.5</v>
+        <v>1869.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2057,11 +2067,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>3366</v>
+        <v>5376</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>677114</v>
+        <v>895366</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6543,12 +6553,22 @@
       <c r="B16" s="27">
         <v>46210</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
+      <c r="C16" s="34">
+        <v>325910</v>
+      </c>
+      <c r="D16" s="34">
+        <v>274485.5</v>
+      </c>
+      <c r="E16" s="31">
+        <v>1255.5</v>
+      </c>
       <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
+      <c r="G16" s="31">
+        <v>2496</v>
+      </c>
+      <c r="H16" s="34">
+        <v>273230</v>
+      </c>
       <c r="I16" s="31"/>
       <c r="J16" s="34"/>
       <c r="K16" s="32"/>
@@ -7297,15 +7317,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>776988.5</v>
+        <v>1102898.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>653909</v>
+        <v>928394.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>1539</v>
+        <v>2794.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7313,11 +7333,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>4902</v>
+        <v>7398</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>652887</v>
+        <v>926117</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11806,12 +11826,22 @@
       <c r="B16" s="27">
         <v>46210</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
+      <c r="C16" s="34">
+        <v>287132</v>
+      </c>
+      <c r="D16" s="34">
+        <v>243548.75</v>
+      </c>
+      <c r="E16" s="31">
+        <v>2143.75</v>
+      </c>
       <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
+      <c r="G16" s="31">
+        <v>1824</v>
+      </c>
+      <c r="H16" s="34">
+        <v>241405</v>
+      </c>
       <c r="I16" s="31"/>
       <c r="J16" s="34"/>
       <c r="K16" s="32"/>
@@ -12560,15 +12590,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1289226</v>
+        <v>1576358</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1101966.25</v>
+        <v>1345515</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>55.5</v>
+        <v>2199.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12576,11 +12606,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>6048</v>
+        <v>7872</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1102025</v>
+        <v>1343430</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FE04124-5088-4D53-ABC2-6EA73AB41444}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B09879-A80B-4A03-BF6E-01E31972B923}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -66,6 +66,32 @@
           <t xml:space="preserve">
 SOUND CHECK
 S.I NO 11198
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{9A3CA438-2914-421D-B98E-FBA124A2BA24}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+S.I NO 11030
 </t>
         </r>
       </text>
@@ -190,7 +216,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +328,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1325,13 +1364,23 @@
       <c r="B17" s="27">
         <v>46211</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
+      <c r="C17" s="34">
+        <v>290058.5</v>
+      </c>
+      <c r="D17" s="34">
+        <v>200363</v>
+      </c>
+      <c r="E17" s="31">
+        <v>115</v>
+      </c>
       <c r="F17" s="31"/>
       <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
+      <c r="H17" s="34">
+        <v>200248</v>
+      </c>
+      <c r="I17" s="31">
+        <v>48345</v>
+      </c>
       <c r="J17" s="34"/>
       <c r="K17" s="32"/>
       <c r="L17" s="1"/>
@@ -2051,15 +2100,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1121485.5</v>
+        <v>1411544</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>688883.5</v>
+        <v>889246.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>1869.5</v>
+        <v>1984.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2071,11 +2120,11 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>895366</v>
+        <v>1095614</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>43785</v>
+        <v>92130</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -6591,12 +6640,22 @@
       <c r="B17" s="27">
         <v>46211</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
+      <c r="C17" s="34">
+        <v>217925</v>
+      </c>
+      <c r="D17" s="34">
+        <v>185540</v>
+      </c>
       <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
+      <c r="F17" s="34">
+        <v>52</v>
+      </c>
+      <c r="G17" s="31">
+        <v>1206</v>
+      </c>
+      <c r="H17" s="34">
+        <v>185592</v>
+      </c>
       <c r="I17" s="31"/>
       <c r="J17" s="34"/>
       <c r="K17" s="32"/>
@@ -7317,11 +7376,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1102898.5</v>
+        <v>1320823.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>928394.5</v>
+        <v>1113934.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7329,15 +7388,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>517</v>
+        <v>569</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>7398</v>
+        <v>8604</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>926117</v>
+        <v>1111709</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11864,12 +11923,20 @@
       <c r="B17" s="27">
         <v>46211</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
+      <c r="C17" s="34">
+        <v>349413</v>
+      </c>
+      <c r="D17" s="34">
+        <v>305021.5</v>
+      </c>
+      <c r="E17" s="31">
+        <v>2129.5</v>
+      </c>
       <c r="F17" s="31"/>
       <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
+      <c r="H17" s="34">
+        <v>302892</v>
+      </c>
       <c r="I17" s="31"/>
       <c r="J17" s="34"/>
       <c r="K17" s="32"/>
@@ -12590,15 +12657,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1576358</v>
+        <v>1925771</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1345515</v>
+        <v>1650536.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2199.25</v>
+        <v>4328.75</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12610,7 +12677,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1343430</v>
+        <v>1646322</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B09879-A80B-4A03-BF6E-01E31972B923}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A088F3-BC33-4F9E-87FD-A2C1D0F679B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -11865,7 +11865,9 @@
       </c>
       <c r="I15" s="31"/>
       <c r="J15" s="34"/>
-      <c r="K15" s="32"/>
+      <c r="K15" s="32">
+        <v>50</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -12689,7 +12691,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A088F3-BC33-4F9E-87FD-A2C1D0F679B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDB400A-B625-42FE-9FF8-A5026F1F2B20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -93,6 +93,56 @@
 SOUND CHECK
 S.I NO 11030
 </t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{89D6F533-4651-428F-8183-5752565AD876}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+SI NO. 11033</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{5A1C2166-8717-4896-B321-FA19CB2FD9F0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+SI NO. 11180</t>
         </r>
       </text>
     </comment>
@@ -1402,14 +1452,26 @@
       <c r="B18" s="27">
         <v>46212</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="31"/>
+      <c r="C18" s="32">
+        <v>295573</v>
+      </c>
+      <c r="D18" s="32">
+        <v>240035.5</v>
+      </c>
+      <c r="E18" s="31">
+        <v>274.5</v>
+      </c>
       <c r="F18" s="31"/>
       <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
+      <c r="H18" s="32">
+        <v>239761</v>
+      </c>
+      <c r="I18" s="31">
+        <v>95886</v>
+      </c>
+      <c r="J18" s="31">
+        <v>84261</v>
+      </c>
       <c r="K18" s="31"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2100,15 +2162,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1411544</v>
+        <v>1707117</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>889246.5</v>
+        <v>1129282</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>1984.5</v>
+        <v>2259</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2120,15 +2182,15 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1095614</v>
+        <v>1335375</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>92130</v>
+        <v>188016</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>84261</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -6678,12 +6740,22 @@
       <c r="B18" s="27">
         <v>46212</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="31"/>
+      <c r="C18" s="32">
+        <v>236707</v>
+      </c>
+      <c r="D18" s="32">
+        <v>200869</v>
+      </c>
+      <c r="E18" s="31">
+        <v>204</v>
+      </c>
       <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
+      <c r="G18" s="31">
+        <v>1296</v>
+      </c>
+      <c r="H18" s="32">
+        <v>200665</v>
+      </c>
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
@@ -7376,15 +7448,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1320823.5</v>
+        <v>1557530.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1113934.5</v>
+        <v>1314803.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2794.5</v>
+        <v>2998.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7392,11 +7464,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>8604</v>
+        <v>9900</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1111709</v>
+        <v>1312374</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11961,12 +12033,22 @@
       <c r="B18" s="27">
         <v>46212</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
+      <c r="C18" s="32">
+        <v>112831.5</v>
+      </c>
+      <c r="D18" s="32">
+        <v>94338</v>
+      </c>
       <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
+      <c r="F18" s="32">
+        <v>2094</v>
+      </c>
+      <c r="G18" s="31">
+        <v>300</v>
+      </c>
+      <c r="H18" s="32">
+        <v>96432</v>
+      </c>
       <c r="I18" s="31"/>
       <c r="J18" s="31"/>
       <c r="K18" s="31"/>
@@ -12659,11 +12741,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1925771</v>
+        <v>2038602.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1650536.5</v>
+        <v>1744874.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12671,15 +12753,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>114.25</v>
+        <v>2208.25</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>7872</v>
+        <v>8172</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1646322</v>
+        <v>1742754</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDB400A-B625-42FE-9FF8-A5026F1F2B20}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC823609-1EE7-4234-8D3B-ECAC759B3BBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC823609-1EE7-4234-8D3B-ECAC759B3BBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CB18E5-797C-4F2D-9127-D489FC3BCCB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1492,15 +1492,17 @@
       <c r="B19" s="27">
         <v>46213</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
+      <c r="C19" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="45"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -6193,7 +6195,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C10:K10"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C42:K42"/>
@@ -6201,6 +6203,7 @@
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C35:K35"/>
     <mergeCell ref="C13:K13"/>
+    <mergeCell ref="C19:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6778,15 +6781,17 @@
       <c r="B19" s="27">
         <v>46213</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
+      <c r="C19" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="45"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -11479,7 +11484,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C11:K11"/>
@@ -11487,6 +11492,7 @@
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C35:K35"/>
+    <mergeCell ref="C19:K19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -12071,12 +12077,22 @@
       <c r="B19" s="27">
         <v>46213</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
+      <c r="C19" s="32">
+        <v>249944.5</v>
+      </c>
+      <c r="D19" s="32">
+        <v>211759.25</v>
+      </c>
       <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="34"/>
+      <c r="F19" s="34">
+        <v>12.75</v>
+      </c>
+      <c r="G19" s="31">
+        <v>942</v>
+      </c>
+      <c r="H19" s="34">
+        <v>211772</v>
+      </c>
       <c r="I19" s="31"/>
       <c r="J19" s="31"/>
       <c r="K19" s="31"/>
@@ -12741,11 +12757,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2038602.5</v>
+        <v>2288547</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1744874.5</v>
+        <v>1956633.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12753,15 +12769,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>2208.25</v>
+        <v>2221</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>8172</v>
+        <v>9114</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1742754</v>
+        <v>1954526</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CB18E5-797C-4F2D-9127-D489FC3BCCB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CAA5BB-8562-4A5D-9543-D687E0764DAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1522,15 +1522,17 @@
       <c r="B20" s="27">
         <v>46214</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
+      <c r="C20" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="45"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -1580,12 +1582,22 @@
       <c r="B22" s="27">
         <v>46216</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
+      <c r="C22" s="32">
+        <v>265548.5</v>
+      </c>
+      <c r="D22" s="32">
+        <v>226385.75</v>
+      </c>
+      <c r="E22" s="31">
+        <v>300.75</v>
+      </c>
       <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
+      <c r="G22" s="31">
+        <v>1356</v>
+      </c>
+      <c r="H22" s="32">
+        <v>226085</v>
+      </c>
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
@@ -2164,15 +2176,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1707117</v>
+        <v>1972665.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1129282</v>
+        <v>1355667.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2259</v>
+        <v>2559.75</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2180,11 +2192,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>5376</v>
+        <v>6732</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1335375</v>
+        <v>1561460</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6195,7 +6207,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C10:K10"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C42:K42"/>
@@ -6204,6 +6216,7 @@
     <mergeCell ref="C35:K35"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C19:K19"/>
+    <mergeCell ref="C20:K20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" r:id="rId1"/>
@@ -6811,15 +6824,17 @@
       <c r="B20" s="27">
         <v>46214</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
+      <c r="C20" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="45"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -6869,12 +6884,22 @@
       <c r="B22" s="27">
         <v>46216</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
+      <c r="C22" s="32">
+        <v>264783</v>
+      </c>
+      <c r="D22" s="32">
+        <v>223640.25</v>
+      </c>
+      <c r="E22" s="31">
+        <v>149.25</v>
+      </c>
       <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
+      <c r="G22" s="31">
+        <v>1548</v>
+      </c>
+      <c r="H22" s="32">
+        <v>223491</v>
+      </c>
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
@@ -7453,15 +7478,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1557530.5</v>
+        <v>1822313.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1314803.5</v>
+        <v>1538443.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2998.5</v>
+        <v>3147.75</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7469,11 +7494,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>9900</v>
+        <v>11448</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1312374</v>
+        <v>1535865</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11484,7 +11509,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C11:K11"/>
@@ -11493,6 +11518,7 @@
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C35:K35"/>
     <mergeCell ref="C19:K19"/>
+    <mergeCell ref="C20:K20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -12115,15 +12141,17 @@
       <c r="B20" s="27">
         <v>46214</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
+      <c r="C20" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="45"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -12173,12 +12201,22 @@
       <c r="B22" s="27">
         <v>46216</v>
       </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
+      <c r="C22" s="32">
+        <v>386726.5</v>
+      </c>
+      <c r="D22" s="32">
+        <v>322822.75</v>
+      </c>
+      <c r="E22" s="31">
+        <v>3522.75</v>
+      </c>
       <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
+      <c r="G22" s="31">
+        <v>1296</v>
+      </c>
+      <c r="H22" s="32">
+        <v>319300</v>
+      </c>
       <c r="I22" s="32"/>
       <c r="J22" s="32"/>
       <c r="K22" s="32"/>
@@ -12757,15 +12795,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2288547</v>
+        <v>2675273.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1956633.75</v>
+        <v>2279456.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>4328.75</v>
+        <v>7851.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12773,11 +12811,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>9114</v>
+        <v>10410</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1954526</v>
+        <v>2273826</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -16788,13 +16826,14 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C14:K14"/>
     <mergeCell ref="C21:K21"/>
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C35:K35"/>
+    <mergeCell ref="C20:K20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CAA5BB-8562-4A5D-9543-D687E0764DAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9BEE58-A422-450C-882A-739C0D9DAD10}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -1620,12 +1620,22 @@
       <c r="B23" s="27">
         <v>46217</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
+      <c r="C23" s="32">
+        <v>263812.5</v>
+      </c>
+      <c r="D23" s="32">
+        <v>222004.5</v>
+      </c>
       <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
+      <c r="F23" s="32">
+        <v>462.5</v>
+      </c>
+      <c r="G23" s="31">
+        <v>1404</v>
+      </c>
+      <c r="H23" s="32">
+        <v>222467</v>
+      </c>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
       <c r="K23" s="32"/>
@@ -2176,11 +2186,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1972665.5</v>
+        <v>2236478</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1355667.75</v>
+        <v>1577672.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -2188,15 +2198,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>2881.4300000000003</v>
+        <v>3343.9300000000003</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>6732</v>
+        <v>8136</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1561460</v>
+        <v>1783927</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -6922,12 +6932,22 @@
       <c r="B23" s="27">
         <v>46217</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
+      <c r="C23" s="32">
+        <v>2444360.33</v>
+      </c>
+      <c r="D23" s="32">
+        <v>205234.33</v>
+      </c>
+      <c r="E23" s="31">
+        <v>193.33</v>
+      </c>
       <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
+      <c r="G23" s="31">
+        <v>1296</v>
+      </c>
+      <c r="H23" s="32">
+        <v>205041</v>
+      </c>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
       <c r="K23" s="32"/>
@@ -7478,15 +7498,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>1822313.5</v>
+        <v>4266673.83</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1538443.75</v>
+        <v>1743678.08</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3147.75</v>
+        <v>3341.08</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7494,11 +7514,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>11448</v>
+        <v>12744</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1535865</v>
+        <v>1740906</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12239,15 +12259,27 @@
       <c r="B23" s="27">
         <v>46217</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
+      <c r="C23" s="32">
+        <v>226895</v>
+      </c>
+      <c r="D23" s="32">
+        <v>191038.5</v>
+      </c>
       <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
+      <c r="F23" s="32">
+        <v>1106.5</v>
+      </c>
+      <c r="G23" s="31">
+        <v>1446</v>
+      </c>
+      <c r="H23" s="32">
+        <v>192145</v>
+      </c>
       <c r="I23" s="32"/>
       <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="K23" s="32">
+        <v>50</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="7"/>
@@ -12795,11 +12827,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2675273.5</v>
+        <v>2902168.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2279456.5</v>
+        <v>2470495</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12807,15 +12839,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>2221</v>
+        <v>3327.5</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>10410</v>
+        <v>11856</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2273826</v>
+        <v>2465971</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12827,7 +12859,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9BEE58-A422-450C-882A-739C0D9DAD10}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D30D50-C363-4A42-B4C7-4406246B948A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -143,6 +143,31 @@
           <t xml:space="preserve">
 BALWARTE
 SI NO. 11180</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{A4D2DD5B-105B-439E-8A47-60C190A1E514}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 11463</t>
         </r>
       </text>
     </comment>
@@ -1658,13 +1683,23 @@
       <c r="B24" s="27">
         <v>46218</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
+      <c r="C24" s="32">
+        <v>230785.5</v>
+      </c>
+      <c r="D24" s="32">
+        <v>138191</v>
+      </c>
       <c r="E24" s="31"/>
-      <c r="F24" s="34"/>
+      <c r="F24" s="34">
+        <v>115</v>
+      </c>
       <c r="G24" s="31"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="31"/>
+      <c r="H24" s="34">
+        <v>138306</v>
+      </c>
+      <c r="I24" s="31">
+        <v>62203</v>
+      </c>
       <c r="J24" s="34"/>
       <c r="K24" s="34"/>
       <c r="L24" s="1"/>
@@ -2186,11 +2221,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2236478</v>
+        <v>2467263.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1577672.25</v>
+        <v>1715863.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -2198,7 +2233,7 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>3343.9300000000003</v>
+        <v>3458.9300000000003</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
@@ -2206,11 +2241,11 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1783927</v>
+        <v>1922233</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>188016</v>
+        <v>250219</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -6970,12 +7005,20 @@
       <c r="B24" s="27">
         <v>46218</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="31"/>
+      <c r="C24" s="32">
+        <v>151113.32999999999</v>
+      </c>
+      <c r="D24" s="32">
+        <v>130290.33</v>
+      </c>
+      <c r="E24" s="31">
+        <v>360.33</v>
+      </c>
       <c r="F24" s="34"/>
       <c r="G24" s="31"/>
-      <c r="H24" s="34"/>
+      <c r="H24" s="34">
+        <v>130290.33</v>
+      </c>
       <c r="I24" s="31"/>
       <c r="J24" s="34"/>
       <c r="K24" s="34"/>
@@ -7498,15 +7541,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4266673.83</v>
+        <v>4417787.16</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1743678.08</v>
+        <v>1873968.4100000001</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3341.08</v>
+        <v>3701.41</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7518,7 +7561,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1740906</v>
+        <v>1871196.33</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12299,12 +12342,22 @@
       <c r="B24" s="27">
         <v>46218</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="31"/>
+      <c r="C24" s="32">
+        <v>341541</v>
+      </c>
+      <c r="D24" s="32">
+        <v>279441.75</v>
+      </c>
+      <c r="E24" s="31">
+        <v>2872.75</v>
+      </c>
       <c r="F24" s="34"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="34"/>
+      <c r="G24" s="31">
+        <v>1896</v>
+      </c>
+      <c r="H24" s="34">
+        <v>276569</v>
+      </c>
       <c r="I24" s="31"/>
       <c r="J24" s="34"/>
       <c r="K24" s="34"/>
@@ -12827,15 +12880,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2902168.5</v>
+        <v>3243709.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2470495</v>
+        <v>2749936.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>7851.5</v>
+        <v>10724.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12843,11 +12896,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>11856</v>
+        <v>13752</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2465971</v>
+        <v>2742540</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D30D50-C363-4A42-B4C7-4406246B948A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94F4F37-9D05-4516-879B-5F61BC620A04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -78,7 +78,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -87,7 +87,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 SOUND CHECK
@@ -104,7 +104,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -113,7 +113,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 BALWARTE
@@ -129,7 +129,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -138,7 +138,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 BALWARTE
@@ -154,7 +154,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -163,7 +163,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 SOUND CHECK
@@ -291,7 +291,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,19 +403,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1721,12 +1708,22 @@
       <c r="B25" s="27">
         <v>46219</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
+      <c r="C25" s="32">
+        <v>249733</v>
+      </c>
+      <c r="D25" s="32">
+        <v>213767.5</v>
+      </c>
       <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
+      <c r="F25" s="32">
+        <v>1740.5</v>
+      </c>
+      <c r="G25" s="31">
+        <v>684</v>
+      </c>
+      <c r="H25" s="32">
+        <v>215508</v>
+      </c>
       <c r="I25" s="31"/>
       <c r="J25" s="32"/>
       <c r="K25" s="31"/>
@@ -2221,11 +2218,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2467263.5</v>
+        <v>2716996.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1715863.25</v>
+        <v>1929630.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -2233,15 +2230,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>3458.9300000000003</v>
+        <v>5199.43</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>8136</v>
+        <v>8820</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1922233</v>
+        <v>2137741</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7041,12 +7038,22 @@
       <c r="B25" s="27">
         <v>46219</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="31"/>
+      <c r="C25" s="32">
+        <v>278011.66666666669</v>
+      </c>
+      <c r="D25" s="32">
+        <v>244719.16666666669</v>
+      </c>
+      <c r="E25" s="31">
+        <v>84.17</v>
+      </c>
       <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
+      <c r="G25" s="31">
+        <v>2004</v>
+      </c>
+      <c r="H25" s="32">
+        <v>244635</v>
+      </c>
       <c r="I25" s="31"/>
       <c r="J25" s="32"/>
       <c r="K25" s="31"/>
@@ -7541,15 +7548,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4417787.16</v>
+        <v>4695798.8266666671</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1873968.4100000001</v>
+        <v>2118687.5766666667</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3701.41</v>
+        <v>3785.58</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7557,11 +7564,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>12744</v>
+        <v>14748</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>1871196.33</v>
+        <v>2115831.33</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12380,15 +12387,28 @@
       <c r="B25" s="27">
         <v>46219</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
+      <c r="C25" s="32">
+        <v>142129.5</v>
+      </c>
+      <c r="D25" s="32">
+        <v>121441.5</v>
+      </c>
       <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="32"/>
+      <c r="F25" s="32">
+        <v>2442.5</v>
+      </c>
+      <c r="G25" s="31">
+        <v>780</v>
+      </c>
+      <c r="H25" s="32">
+        <v>123884</v>
+      </c>
       <c r="I25" s="31"/>
       <c r="J25" s="32"/>
-      <c r="K25" s="31"/>
+      <c r="K25" s="32">
+        <f>50+100</f>
+        <v>150</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="7"/>
@@ -12880,11 +12900,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3243709.5</v>
+        <v>3385839</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2749936.75</v>
+        <v>2871378.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -12892,15 +12912,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>3327.5</v>
+        <v>5770</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>13752</v>
+        <v>14532</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2742540</v>
+        <v>2866424</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12912,7 +12932,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B94F4F37-9D05-4516-879B-5F61BC620A04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16058110-92FB-45D9-B0B4-C730FCE1B5C0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -171,6 +171,56 @@
         </r>
       </text>
     </comment>
+    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{CA1086BA-8C22-4706-8DC5-A44209D61B15}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+SI NO. 11426</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J26" authorId="0" shapeId="0" xr:uid="{0313F5C5-A99F-4CAC-AA16-AA6BB50CCFA3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+BALWARTE
+SI NO. 11033</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -291,7 +341,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,6 +453,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1746,14 +1809,29 @@
       <c r="B26" s="27">
         <v>46220</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="31"/>
+      <c r="C26" s="32">
+        <v>476545</v>
+      </c>
+      <c r="D26" s="32">
+        <v>421468.75</v>
+      </c>
+      <c r="E26" s="31">
+        <v>311.75</v>
+      </c>
       <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
+      <c r="G26" s="31">
+        <v>2622</v>
+      </c>
+      <c r="H26" s="32">
+        <v>421157</v>
+      </c>
+      <c r="I26" s="31">
+        <f>82890</f>
+        <v>82890</v>
+      </c>
+      <c r="J26" s="31">
+        <v>95886</v>
+      </c>
       <c r="K26" s="31"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -2218,15 +2296,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>2716996.5</v>
+        <v>3193541.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>1929630.75</v>
+        <v>2351099.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2559.75</v>
+        <v>2871.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2234,19 +2312,19 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>8820</v>
+        <v>11442</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2137741</v>
+        <v>2558898</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>250219</v>
+        <v>333109</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>84261</v>
+        <v>180147</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -7076,12 +7154,22 @@
       <c r="B26" s="27">
         <v>46220</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
+      <c r="C26" s="32">
+        <v>270113.33</v>
+      </c>
+      <c r="D26" s="32">
+        <v>227409.83</v>
+      </c>
       <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
+      <c r="F26" s="32">
+        <v>72.17</v>
+      </c>
+      <c r="G26" s="31">
+        <v>972</v>
+      </c>
+      <c r="H26" s="32">
+        <v>227482</v>
+      </c>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
@@ -7548,11 +7636,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4695798.8266666671</v>
+        <v>4965912.1566666672</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2118687.5766666667</v>
+        <v>2346097.4066666667</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7560,15 +7648,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>569</v>
+        <v>641.16999999999996</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>14748</v>
+        <v>15720</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2115831.33</v>
+        <v>2343313.33</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12428,12 +12516,22 @@
       <c r="B26" s="27">
         <v>46220</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="31"/>
+      <c r="C26" s="32">
+        <v>507045</v>
+      </c>
+      <c r="D26" s="32">
+        <v>442359</v>
+      </c>
+      <c r="E26" s="31">
+        <v>65</v>
+      </c>
       <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="32"/>
+      <c r="G26" s="31">
+        <v>2592</v>
+      </c>
+      <c r="H26" s="32">
+        <v>442294</v>
+      </c>
       <c r="I26" s="31"/>
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
@@ -12900,15 +12998,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3385839</v>
+        <v>3892884</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2871378.25</v>
+        <v>3313737.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>10724.25</v>
+        <v>10789.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -12916,11 +13014,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>14532</v>
+        <v>17124</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2866424</v>
+        <v>3308718</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16058110-92FB-45D9-B0B4-C730FCE1B5C0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0682A68-0064-4555-95B6-CC32F9310F63}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -221,12 +221,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{BBAC9318-A30D-4FC5-800F-7EEA5DCF1F98}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+S.I NO 11463</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -1859,7 +1884,9 @@
       <c r="G27" s="42"/>
       <c r="H27" s="33"/>
       <c r="I27" s="42"/>
-      <c r="J27" s="33"/>
+      <c r="J27" s="42">
+        <v>62203</v>
+      </c>
       <c r="K27" s="30"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -1910,12 +1937,22 @@
       <c r="B29" s="27">
         <v>46223</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="13"/>
+      <c r="C29" s="11">
+        <v>446877</v>
+      </c>
+      <c r="D29" s="37">
+        <v>381656.25</v>
+      </c>
+      <c r="E29" s="13">
+        <v>8.25</v>
+      </c>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="33"/>
+      <c r="G29" s="42">
+        <v>1656</v>
+      </c>
+      <c r="H29" s="33">
+        <v>381648</v>
+      </c>
       <c r="I29" s="42"/>
       <c r="J29" s="33"/>
       <c r="K29" s="30"/>
@@ -2296,15 +2333,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3193541.5</v>
+        <v>3640418.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2351099.5</v>
+        <v>2732755.75</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2871.5</v>
+        <v>2879.75</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2312,11 +2349,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>11442</v>
+        <v>13098</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2558898</v>
+        <v>2940546</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -2324,7 +2361,7 @@
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>180147</v>
+        <v>242350</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -7192,15 +7229,17 @@
       <c r="B27" s="27">
         <v>46221</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="30"/>
+      <c r="C27" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="7"/>
@@ -7250,12 +7289,22 @@
       <c r="B29" s="27">
         <v>46223</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="13"/>
+      <c r="C29" s="11">
+        <v>283390</v>
+      </c>
+      <c r="D29" s="37">
+        <v>238142.5</v>
+      </c>
+      <c r="E29" s="13">
+        <v>721.5</v>
+      </c>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="33"/>
+      <c r="G29" s="42">
+        <v>1776</v>
+      </c>
+      <c r="H29" s="33">
+        <v>237421</v>
+      </c>
       <c r="I29" s="42"/>
       <c r="J29" s="33"/>
       <c r="K29" s="30"/>
@@ -7636,15 +7685,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4965912.1566666672</v>
+        <v>5249302.1566666672</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2346097.4066666667</v>
+        <v>2584239.9066666667</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>3785.58</v>
+        <v>4507.08</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7652,11 +7701,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>15720</v>
+        <v>17496</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2343313.33</v>
+        <v>2580734.33</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11667,7 +11716,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C11:K11"/>
@@ -11677,6 +11726,7 @@
     <mergeCell ref="C35:K35"/>
     <mergeCell ref="C19:K19"/>
     <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C27:K27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -12554,15 +12604,17 @@
       <c r="B27" s="27">
         <v>46221</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="30"/>
+      <c r="C27" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="44"/>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="7"/>
@@ -12612,15 +12664,27 @@
       <c r="B29" s="27">
         <v>46223</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="13"/>
+      <c r="C29" s="11">
+        <v>510270</v>
+      </c>
+      <c r="D29" s="37">
+        <v>435177.25</v>
+      </c>
+      <c r="E29" s="13">
+        <v>145.25</v>
+      </c>
       <c r="F29" s="11"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="33"/>
+      <c r="G29" s="42">
+        <v>1584</v>
+      </c>
+      <c r="H29" s="33">
+        <v>435032</v>
+      </c>
       <c r="I29" s="42"/>
       <c r="J29" s="33"/>
-      <c r="K29" s="30"/>
+      <c r="K29" s="30">
+        <v>50</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="7"/>
@@ -12998,15 +13062,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3892884</v>
+        <v>4403154</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3313737.25</v>
+        <v>3748914.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>10789.25</v>
+        <v>10934.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13014,11 +13078,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>17124</v>
+        <v>18708</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3308718</v>
+        <v>3743750</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13030,7 +13094,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -17029,7 +17093,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C14:K14"/>
@@ -17037,6 +17101,7 @@
     <mergeCell ref="C28:K28"/>
     <mergeCell ref="C35:K35"/>
     <mergeCell ref="C20:K20"/>
+    <mergeCell ref="C27:K27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0682A68-0064-4555-95B6-CC32F9310F63}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ADE60E-7E6A-4799-9B08-94C3639492D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -243,6 +243,40 @@
           <t xml:space="preserve">
 SOUND CHECK
 S.I NO 11463</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="K30" authorId="0" shapeId="0" xr:uid="{A4516D3E-FA50-4CA0-9404-5EB8FC48E51A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+INCENTIVES HENSON</t>
         </r>
       </text>
     </comment>
@@ -1975,12 +2009,20 @@
       <c r="B30" s="27">
         <v>46224</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="37"/>
+      <c r="C30" s="11">
+        <v>240956.33</v>
+      </c>
+      <c r="D30" s="37">
+        <v>205623.83</v>
+      </c>
       <c r="E30" s="13"/>
-      <c r="F30" s="11"/>
+      <c r="F30" s="11">
+        <v>48.17</v>
+      </c>
       <c r="G30" s="42"/>
-      <c r="H30" s="33"/>
+      <c r="H30" s="33">
+        <v>205672</v>
+      </c>
       <c r="I30" s="42"/>
       <c r="J30" s="33"/>
       <c r="K30" s="30"/>
@@ -2333,11 +2375,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3640418.5</v>
+        <v>3881374.83</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2732755.75</v>
+        <v>2938379.58</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -2345,7 +2387,7 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>5199.43</v>
+        <v>5247.6</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
@@ -2353,7 +2395,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2940546</v>
+        <v>3146218</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7327,12 +7369,22 @@
       <c r="B30" s="27">
         <v>46224</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="13"/>
+      <c r="C30" s="11">
+        <v>151595</v>
+      </c>
+      <c r="D30" s="37">
+        <v>124368.5</v>
+      </c>
+      <c r="E30" s="13">
+        <v>234.5</v>
+      </c>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="33"/>
+      <c r="G30" s="42">
+        <v>252</v>
+      </c>
+      <c r="H30" s="33">
+        <v>124134</v>
+      </c>
       <c r="I30" s="42"/>
       <c r="J30" s="33"/>
       <c r="K30" s="30"/>
@@ -7685,15 +7737,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5249302.1566666672</v>
+        <v>5400897.1566666672</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2584239.9066666667</v>
+        <v>2708608.4066666667</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>4507.08</v>
+        <v>4741.58</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7701,11 +7753,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>17496</v>
+        <v>17748</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2580734.33</v>
+        <v>2704868.33</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -11734,7 +11786,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E737051-E669-4C2F-B4D4-F8B394C392B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E737051-E669-4C2F-B4D4-F8B394C392B3}">
   <dimension ref="A1:V279"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -12704,15 +12756,27 @@
       <c r="B30" s="27">
         <v>46224</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="13"/>
+      <c r="C30" s="11">
+        <v>344940</v>
+      </c>
+      <c r="D30" s="37">
+        <v>262971.75</v>
+      </c>
+      <c r="E30" s="13">
+        <v>104.75</v>
+      </c>
       <c r="F30" s="11"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="33"/>
+      <c r="G30" s="42">
+        <v>1104</v>
+      </c>
+      <c r="H30" s="33">
+        <v>262867</v>
+      </c>
       <c r="I30" s="42"/>
       <c r="J30" s="33"/>
-      <c r="K30" s="30"/>
+      <c r="K30" s="30">
+        <v>24757.5</v>
+      </c>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="7"/>
@@ -13062,15 +13126,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4403154</v>
+        <v>4748094</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3748914.5</v>
+        <v>4011886.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>10934.5</v>
+        <v>11039.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13078,11 +13142,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>18708</v>
+        <v>19812</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3743750</v>
+        <v>4006617</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13094,7 +13158,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>300</v>
+        <v>25057.5</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -17105,6 +17169,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ADE60E-7E6A-4799-9B08-94C3639492D5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE31D3FE-DD58-48C5-8547-A40E62A4BC4D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -2045,15 +2045,25 @@
       <c r="B31" s="27">
         <v>46225</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="13"/>
+      <c r="C31" s="11">
+        <v>222100.5</v>
+      </c>
+      <c r="D31" s="37">
+        <v>189759.14</v>
+      </c>
+      <c r="E31" s="13">
+        <v>1328.14</v>
+      </c>
       <c r="F31" s="11"/>
       <c r="G31" s="42"/>
-      <c r="H31" s="33"/>
+      <c r="H31" s="33">
+        <v>188431</v>
+      </c>
       <c r="I31" s="42"/>
       <c r="J31" s="33"/>
-      <c r="K31" s="30"/>
+      <c r="K31" s="30">
+        <v>92.86</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="17"/>
@@ -2375,15 +2385,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>3881374.83</v>
+        <v>4103475.33</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2938379.58</v>
+        <v>3128138.72</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>2879.75</v>
+        <v>4207.8900000000003</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2395,7 +2405,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3146218</v>
+        <v>3334649</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -2407,7 +2417,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>127.68</v>
+        <v>220.54000000000002</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -7407,12 +7417,22 @@
       <c r="B31" s="27">
         <v>46225</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="13"/>
+      <c r="C31" s="11">
+        <v>230482.54</v>
+      </c>
+      <c r="D31" s="37">
+        <v>194682.04</v>
+      </c>
+      <c r="E31" s="13">
+        <v>299.04000000000002</v>
+      </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="33"/>
+      <c r="G31" s="42">
+        <v>1668</v>
+      </c>
+      <c r="H31" s="33">
+        <v>194383</v>
+      </c>
       <c r="I31" s="42"/>
       <c r="J31" s="33"/>
       <c r="K31" s="30"/>
@@ -7737,15 +7757,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5400897.1566666672</v>
+        <v>5631379.6966666672</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2708608.4066666667</v>
+        <v>2903290.4466666668</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>4741.58</v>
+        <v>5040.62</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7753,11 +7773,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>17748</v>
+        <v>19416</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2704868.33</v>
+        <v>2899251.33</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12796,12 +12816,20 @@
       <c r="B31" s="27">
         <v>46225</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="13"/>
+      <c r="C31" s="11">
+        <v>408168</v>
+      </c>
+      <c r="D31" s="37">
+        <v>371172.75</v>
+      </c>
+      <c r="E31" s="13">
+        <v>0.75</v>
+      </c>
       <c r="F31" s="11"/>
       <c r="G31" s="42"/>
-      <c r="H31" s="33"/>
+      <c r="H31" s="33">
+        <v>371172</v>
+      </c>
       <c r="I31" s="42"/>
       <c r="J31" s="33"/>
       <c r="K31" s="30"/>
@@ -13126,15 +13154,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4748094</v>
+        <v>5156262</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4011886.25</v>
+        <v>4383059</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>11039.25</v>
+        <v>11040</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13146,7 +13174,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4006617</v>
+        <v>4377789</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE31D3FE-DD58-48C5-8547-A40E62A4BC4D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15B5BA7-9E96-4245-A0DA-D47855C09E7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -243,6 +243,31 @@
           <t xml:space="preserve">
 SOUND CHECK
 S.I NO 11463</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{EA416575-FA29-4F4E-8582-524163DB6FD5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 11485</t>
         </r>
       </text>
     </comment>
@@ -2083,13 +2108,25 @@
       <c r="B32" s="27">
         <v>46226</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="31"/>
+      <c r="C32" s="32">
+        <v>282218.17</v>
+      </c>
+      <c r="D32" s="32">
+        <v>198223.17</v>
+      </c>
+      <c r="E32" s="31">
+        <v>102.17</v>
+      </c>
       <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="31"/>
+      <c r="G32" s="31">
+        <v>1296</v>
+      </c>
+      <c r="H32" s="32">
+        <v>198121</v>
+      </c>
+      <c r="I32" s="31">
+        <v>38920</v>
+      </c>
       <c r="J32" s="31"/>
       <c r="K32" s="31"/>
       <c r="L32" s="1"/>
@@ -2385,15 +2422,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4103475.33</v>
+        <v>4385693.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3128138.72</v>
+        <v>3326361.89</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>4207.8900000000003</v>
+        <v>4310.0600000000004</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2401,15 +2438,15 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>13098</v>
+        <v>14394</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3334649</v>
+        <v>3532770</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>333109</v>
+        <v>372029</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -7455,12 +7492,22 @@
       <c r="B32" s="27">
         <v>46226</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="31"/>
+      <c r="C32" s="32">
+        <v>223968.88</v>
+      </c>
+      <c r="D32" s="32">
+        <v>189405.13</v>
+      </c>
+      <c r="E32" s="31">
+        <v>835.13</v>
+      </c>
       <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32"/>
+      <c r="G32" s="31">
+        <v>1008</v>
+      </c>
+      <c r="H32" s="32">
+        <v>188570</v>
+      </c>
       <c r="I32" s="31"/>
       <c r="J32" s="31"/>
       <c r="K32" s="31"/>
@@ -7757,15 +7804,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5631379.6966666672</v>
+        <v>5855348.5766666671</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>2903290.4466666668</v>
+        <v>3092695.5766666667</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>5040.62</v>
+        <v>5875.75</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7773,11 +7820,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>19416</v>
+        <v>20424</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>2899251.33</v>
+        <v>3087821.33</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12852,15 +12899,27 @@
       <c r="B32" s="27">
         <v>46226</v>
       </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
+      <c r="C32" s="32">
+        <v>407248</v>
+      </c>
+      <c r="D32" s="32">
+        <v>340907</v>
+      </c>
       <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="32"/>
+      <c r="F32" s="34">
+        <v>52</v>
+      </c>
+      <c r="G32" s="31">
+        <v>1140</v>
+      </c>
+      <c r="H32" s="32">
+        <v>340959</v>
+      </c>
       <c r="I32" s="31"/>
       <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
+      <c r="K32" s="34">
+        <v>50</v>
+      </c>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="7"/>
@@ -13154,11 +13213,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5156262</v>
+        <v>5563510</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4383059</v>
+        <v>4723966</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -13166,15 +13225,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>5770</v>
+        <v>5822</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>19812</v>
+        <v>20952</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4377789</v>
+        <v>4718748</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13186,7 +13245,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>25057.5</v>
+        <v>25107.5</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B15B5BA7-9E96-4245-A0DA-D47855C09E7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72061135-3DB3-4574-BCCF-E8A44854FE74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -2148,12 +2148,22 @@
       <c r="B33" s="27">
         <v>46227</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
+      <c r="C33" s="32">
+        <v>612830</v>
+      </c>
+      <c r="D33" s="32">
+        <v>570314</v>
+      </c>
       <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32"/>
+      <c r="F33" s="32">
+        <v>7</v>
+      </c>
+      <c r="G33" s="31">
+        <v>4698</v>
+      </c>
+      <c r="H33" s="32">
+        <v>570321</v>
+      </c>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
       <c r="K33" s="31"/>
@@ -2422,11 +2432,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4385693.5</v>
+        <v>4998523.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3326361.89</v>
+        <v>3896675.89</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -2434,15 +2444,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>5247.6</v>
+        <v>5254.6</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>14394</v>
+        <v>19092</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3532770</v>
+        <v>4103091</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -7530,12 +7540,22 @@
       <c r="B33" s="27">
         <v>46227</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
+      <c r="C33" s="32">
+        <v>222577.58</v>
+      </c>
+      <c r="D33" s="32">
+        <v>189464.33</v>
+      </c>
       <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32"/>
+      <c r="F33" s="32">
+        <v>631.66999999999996</v>
+      </c>
+      <c r="G33" s="31">
+        <v>1380</v>
+      </c>
+      <c r="H33" s="32">
+        <v>190096</v>
+      </c>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
       <c r="K33" s="31"/>
@@ -7804,11 +7824,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5855348.5766666671</v>
+        <v>6077926.1566666672</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3092695.5766666667</v>
+        <v>3282159.9066666667</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -7816,15 +7836,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>641.16999999999996</v>
+        <v>1272.8399999999999</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>20424</v>
+        <v>21804</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3087821.33</v>
+        <v>3277917.33</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -12939,12 +12959,22 @@
       <c r="B33" s="27">
         <v>46227</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="32"/>
+      <c r="C33" s="32">
+        <v>505296</v>
+      </c>
+      <c r="D33" s="32">
+        <v>432331.5</v>
+      </c>
+      <c r="E33" s="31">
+        <v>45.5</v>
+      </c>
+      <c r="F33" s="32"/>
+      <c r="G33" s="31">
+        <v>2946</v>
+      </c>
+      <c r="H33" s="32">
+        <v>432286</v>
+      </c>
       <c r="I33" s="31"/>
       <c r="J33" s="31"/>
       <c r="K33" s="31"/>
@@ -13213,15 +13243,15 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5563510</v>
+        <v>6068806</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4723966</v>
+        <v>5156297.5</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
-        <v>11040</v>
+        <v>11085.5</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13229,11 +13259,11 @@
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>20952</v>
+        <v>23898</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4718748</v>
+        <v>5151034</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72061135-3DB3-4574-BCCF-E8A44854FE74}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94231CEF-0164-4ED2-9BCB-AAB9D7F53AA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -271,6 +271,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="J34" authorId="0" shapeId="0" xr:uid="{80F885C1-AC5F-478E-8F44-56A5D826D1B8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 11485</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -310,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="22">
   <si>
     <t>SUNDAY</t>
   </si>
@@ -2186,15 +2211,19 @@
       <c r="B34" s="27">
         <v>46228</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="34"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="32">
+        <v>38920</v>
+      </c>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31">
+        <v>38920</v>
+      </c>
+      <c r="K34" s="31"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="7"/>
@@ -2452,7 +2481,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4103091</v>
+        <v>4142011</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -2460,7 +2489,7 @@
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>242350</v>
+        <v>281270</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
@@ -7578,15 +7607,17 @@
       <c r="B34" s="27">
         <v>46228</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="34"/>
+      <c r="C34" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="44"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="45"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="7"/>
@@ -11855,7 +11886,7 @@
       <c r="G279"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="C42:K42"/>
     <mergeCell ref="C13:K13"/>
     <mergeCell ref="C11:K11"/>
@@ -11866,6 +11897,7 @@
     <mergeCell ref="C19:K19"/>
     <mergeCell ref="C20:K20"/>
     <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C34:K34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -12997,15 +13029,25 @@
       <c r="B34" s="27">
         <v>46228</v>
       </c>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="34"/>
+      <c r="C34" s="32">
+        <v>482911</v>
+      </c>
+      <c r="D34" s="32">
+        <v>442009.75</v>
+      </c>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32">
+        <v>28.25</v>
+      </c>
+      <c r="G34" s="31">
+        <v>1608</v>
+      </c>
+      <c r="H34" s="32">
+        <v>442038</v>
+      </c>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="7"/>
@@ -13243,11 +13285,11 @@
       <c r="B43" s="27"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6068806</v>
+        <v>6551717</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>5156297.5</v>
+        <v>5598307.25</v>
       </c>
       <c r="E43" s="28">
         <f t="shared" si="0"/>
@@ -13255,15 +13297,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>5822</v>
+        <v>5850.25</v>
       </c>
       <c r="G43" s="28">
         <f t="shared" si="0"/>
-        <v>23898</v>
+        <v>25506</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>5151034</v>
+        <v>5593072</v>
       </c>
       <c r="I43" s="28">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94231CEF-0164-4ED2-9BCB-AAB9D7F53AA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F90EABD-27F6-4C9E-A862-CF54FCD644E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -685,7 +685,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -722,9 +722,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -749,7 +746,6 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1112,7 +1108,7 @@
     <col min="3" max="4" width="14.875" customWidth="1"/>
     <col min="5" max="5" width="14.75" customWidth="1"/>
     <col min="6" max="6" width="15" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15" style="40" customWidth="1"/>
+    <col min="7" max="7" width="15" style="38" customWidth="1"/>
     <col min="8" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="14.75" customWidth="1"/>
     <col min="14" max="14" width="13.125" bestFit="1" customWidth="1"/>
@@ -1311,7 +1307,7 @@
       <c r="C9" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="35" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="23" t="s">
@@ -1320,13 +1316,13 @@
       <c r="F9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="39" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="14" t="s">
@@ -1351,20 +1347,20 @@
       <c r="A10" s="10">
         <v>1</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>46204</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="45"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="43"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -1381,28 +1377,28 @@
       <c r="A11" s="10">
         <v>2</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="26">
         <v>46205</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="31">
         <v>298036</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="31">
         <v>206</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32">
+      <c r="E11" s="30"/>
+      <c r="F11" s="31">
         <v>1185.43</v>
       </c>
-      <c r="G11" s="31"/>
-      <c r="H11" s="32">
+      <c r="G11" s="30"/>
+      <c r="H11" s="31">
         <v>206862</v>
       </c>
-      <c r="I11" s="31">
+      <c r="I11" s="30">
         <v>43785</v>
       </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32">
+      <c r="J11" s="31"/>
+      <c r="K11" s="31">
         <v>127.68</v>
       </c>
       <c r="L11" s="1"/>
@@ -1421,28 +1417,28 @@
       <c r="A12" s="10">
         <v>3</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>46206</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="31">
         <v>331281.5</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="31">
         <v>274671.5</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <v>1788.5</v>
       </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="31">
+      <c r="F12" s="31"/>
+      <c r="G12" s="30">
         <v>2040</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="31">
         <v>272883</v>
       </c>
-      <c r="I12" s="31"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -1459,20 +1455,20 @@
       <c r="A13" s="10">
         <v>4</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="26">
         <v>46207</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -1489,20 +1485,20 @@
       <c r="A14" s="10">
         <v>5</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="45"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -1519,28 +1515,28 @@
       <c r="A15" s="10">
         <v>6</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>46209</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="33">
         <v>233857</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <v>195673</v>
       </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="34">
+      <c r="E15" s="30"/>
+      <c r="F15" s="33">
         <v>1696</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="30">
         <v>1326</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="33">
         <v>197369</v>
       </c>
-      <c r="I15" s="31"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="32"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="31"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -1557,28 +1553,28 @@
       <c r="A16" s="10">
         <v>7</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="26">
         <v>46210</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>258311</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <v>218333</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>81</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31">
+      <c r="F16" s="30"/>
+      <c r="G16" s="30">
         <v>2010</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="33">
         <v>218252</v>
       </c>
-      <c r="I16" s="31"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="32"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -1595,28 +1591,28 @@
       <c r="A17" s="10">
         <v>8</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>46211</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>290058.5</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>200363</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>115</v>
       </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="34">
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="33">
         <v>200248</v>
       </c>
-      <c r="I17" s="31">
+      <c r="I17" s="30">
         <v>48345</v>
       </c>
-      <c r="J17" s="34"/>
-      <c r="K17" s="32"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -1633,30 +1629,30 @@
       <c r="A18" s="10">
         <v>9</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="26">
         <v>46212</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="31">
         <v>295573</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="31">
         <v>240035.5</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <v>274.5</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32">
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31">
         <v>239761</v>
       </c>
-      <c r="I18" s="31">
+      <c r="I18" s="30">
         <v>95886</v>
       </c>
-      <c r="J18" s="31">
+      <c r="J18" s="30">
         <v>84261</v>
       </c>
-      <c r="K18" s="31"/>
+      <c r="K18" s="30"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -1673,20 +1669,20 @@
       <c r="A19" s="10">
         <v>10</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="26">
         <v>46213</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="45"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -1703,20 +1699,20 @@
       <c r="A20" s="10">
         <v>11</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>46214</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="45"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="43"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -1733,20 +1729,20 @@
       <c r="A21" s="10">
         <v>12</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="45"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="43"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -1763,28 +1759,28 @@
       <c r="A22" s="10">
         <v>13</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="26">
         <v>46216</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="31">
         <v>265548.5</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="31">
         <v>226385.75</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="30">
         <v>300.75</v>
       </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="31">
+      <c r="F22" s="31"/>
+      <c r="G22" s="30">
         <v>1356</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="31">
         <v>226085</v>
       </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -1801,28 +1797,28 @@
       <c r="A23" s="10">
         <v>14</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="26">
         <v>46217</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="31">
         <v>263812.5</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="31">
         <v>222004.5</v>
       </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32">
+      <c r="E23" s="31"/>
+      <c r="F23" s="31">
         <v>462.5</v>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="30">
         <v>1404</v>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="31">
         <v>222467</v>
       </c>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="7"/>
@@ -1839,28 +1835,28 @@
       <c r="A24" s="10">
         <v>15</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="26">
         <v>46218</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="31">
         <v>230785.5</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="31">
         <v>138191</v>
       </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="34">
+      <c r="E24" s="30"/>
+      <c r="F24" s="33">
         <v>115</v>
       </c>
-      <c r="G24" s="31"/>
-      <c r="H24" s="34">
+      <c r="G24" s="30"/>
+      <c r="H24" s="33">
         <v>138306</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="30">
         <v>62203</v>
       </c>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="7"/>
@@ -1877,28 +1873,28 @@
       <c r="A25" s="10">
         <v>16</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="26">
         <v>46219</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="31">
         <v>249733</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="31">
         <v>213767.5</v>
       </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32">
+      <c r="E25" s="30"/>
+      <c r="F25" s="31">
         <v>1740.5</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="30">
         <v>684</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="31">
         <v>215508</v>
       </c>
-      <c r="I25" s="31"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="31"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="7"/>
@@ -1915,33 +1911,33 @@
       <c r="A26" s="10">
         <v>17</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>46220</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="31">
         <v>476545</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="31">
         <v>421468.75</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="30">
         <v>311.75</v>
       </c>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31">
+      <c r="F26" s="30"/>
+      <c r="G26" s="30">
         <v>2622</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="31">
         <v>421157</v>
       </c>
-      <c r="I26" s="31">
+      <c r="I26" s="30">
         <f>82890</f>
         <v>82890</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="30">
         <v>95886</v>
       </c>
-      <c r="K26" s="31"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="17"/>
@@ -1958,20 +1954,20 @@
       <c r="A27" s="10">
         <v>18</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="26">
         <v>46221</v>
       </c>
       <c r="C27" s="11"/>
-      <c r="D27" s="37"/>
+      <c r="D27" s="36"/>
       <c r="E27" s="13"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42">
+      <c r="G27" s="40"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="40"/>
+      <c r="J27" s="40">
         <v>62203</v>
       </c>
-      <c r="K27" s="30"/>
+      <c r="K27" s="29"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="7"/>
@@ -1988,20 +1984,20 @@
       <c r="A28" s="10">
         <v>19</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="45"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="43"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="7"/>
@@ -2018,28 +2014,28 @@
       <c r="A29" s="10">
         <v>20</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="26">
         <v>46223</v>
       </c>
       <c r="C29" s="11">
         <v>446877</v>
       </c>
-      <c r="D29" s="37">
+      <c r="D29" s="36">
         <v>381656.25</v>
       </c>
       <c r="E29" s="13">
         <v>8.25</v>
       </c>
       <c r="F29" s="11"/>
-      <c r="G29" s="42">
+      <c r="G29" s="40">
         <v>1656</v>
       </c>
-      <c r="H29" s="33">
+      <c r="H29" s="32">
         <v>381648</v>
       </c>
-      <c r="I29" s="42"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="30"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="29"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="7"/>
@@ -2056,26 +2052,26 @@
       <c r="A30" s="10">
         <v>21</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>46224</v>
       </c>
       <c r="C30" s="11">
         <v>240956.33</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="36">
         <v>205623.83</v>
       </c>
       <c r="E30" s="13"/>
       <c r="F30" s="11">
         <v>48.17</v>
       </c>
-      <c r="G30" s="42"/>
-      <c r="H30" s="33">
+      <c r="G30" s="40"/>
+      <c r="H30" s="32">
         <v>205672</v>
       </c>
-      <c r="I30" s="42"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="30"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="29"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="7"/>
@@ -2092,26 +2088,26 @@
       <c r="A31" s="10">
         <v>22</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="26">
         <v>46225</v>
       </c>
       <c r="C31" s="11">
         <v>222100.5</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="36">
         <v>189759.14</v>
       </c>
       <c r="E31" s="13">
         <v>1328.14</v>
       </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="33">
+      <c r="G31" s="40"/>
+      <c r="H31" s="32">
         <v>188431</v>
       </c>
-      <c r="I31" s="42"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="30">
+      <c r="I31" s="40"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="29">
         <v>92.86</v>
       </c>
       <c r="L31" s="1"/>
@@ -2130,30 +2126,30 @@
       <c r="A32" s="10">
         <v>23</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>46226</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="31">
         <v>282218.17</v>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="31">
         <v>198223.17</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="30">
         <v>102.17</v>
       </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31">
+      <c r="F32" s="30"/>
+      <c r="G32" s="30">
         <v>1296</v>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="31">
         <v>198121</v>
       </c>
-      <c r="I32" s="31">
+      <c r="I32" s="30">
         <v>38920</v>
       </c>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="7"/>
@@ -2170,28 +2166,28 @@
       <c r="A33" s="10">
         <v>24</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="26">
         <v>46227</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="31">
         <v>612830</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="31">
         <v>570314</v>
       </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="32">
+      <c r="E33" s="30"/>
+      <c r="F33" s="31">
         <v>7</v>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="30">
         <v>4698</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="31">
         <v>570321</v>
       </c>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="7"/>
@@ -2208,22 +2204,22 @@
       <c r="A34" s="10">
         <v>25</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>46228</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="32">
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="31">
         <v>38920</v>
       </c>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31">
+      <c r="I34" s="30"/>
+      <c r="J34" s="30">
         <v>38920</v>
       </c>
-      <c r="K34" s="31"/>
+      <c r="K34" s="30"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="7"/>
@@ -2240,20 +2236,20 @@
       <c r="A35" s="10">
         <v>26</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C35" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="45"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="43"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="7"/>
@@ -2270,18 +2266,28 @@
       <c r="A36" s="10">
         <v>27</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="26">
         <v>46230</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="30"/>
+      <c r="C36" s="31">
+        <v>260818</v>
+      </c>
+      <c r="D36" s="31">
+        <v>217690.75</v>
+      </c>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31">
+        <v>214.25</v>
+      </c>
+      <c r="G36" s="30">
+        <v>1602</v>
+      </c>
+      <c r="H36" s="31">
+        <v>217905</v>
+      </c>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="7"/>
@@ -2298,18 +2304,18 @@
       <c r="A37" s="10">
         <v>28</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="26">
         <v>46231</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="8"/>
@@ -2326,18 +2332,18 @@
       <c r="A38" s="10">
         <v>29</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="26">
         <v>46232</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="34"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="7"/>
@@ -2354,7 +2360,7 @@
       <c r="A39" s="10">
         <v>30</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="26">
         <v>46233</v>
       </c>
       <c r="C39" s="31"/>
@@ -2382,7 +2388,7 @@
       <c r="A40" s="10">
         <v>31</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="26">
         <v>46234</v>
       </c>
       <c r="C40" s="31"/>
@@ -2408,15 +2414,15 @@
     </row>
     <row r="41" spans="1:22" ht="15">
       <c r="A41" s="10"/>
-      <c r="B41" s="27"/>
+      <c r="B41" s="26"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
       <c r="K41" s="10"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -2432,16 +2438,16 @@
     </row>
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="21"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="43"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -2455,35 +2461,35 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="27"/>
+      <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>4998523.5</v>
+        <v>5259341.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3896675.89</v>
-      </c>
-      <c r="E43" s="28">
+        <v>4114366.64</v>
+      </c>
+      <c r="E43" s="27">
         <f t="shared" si="0"/>
         <v>4310.0600000000004</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>5254.6</v>
-      </c>
-      <c r="G43" s="28">
+        <v>5468.85</v>
+      </c>
+      <c r="G43" s="27">
         <f t="shared" si="0"/>
-        <v>19092</v>
+        <v>20694</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4142011</v>
-      </c>
-      <c r="I43" s="28">
+        <v>4359916</v>
+      </c>
+      <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
         <v>372029</v>
       </c>
@@ -2509,10 +2515,10 @@
     </row>
     <row r="44" spans="1:22" ht="15">
       <c r="A44" s="1"/>
-      <c r="B44" s="29"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
-      <c r="E44" s="25"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
@@ -6519,7 +6525,7 @@
     <col min="3" max="4" width="14.875" customWidth="1"/>
     <col min="5" max="5" width="14.75" customWidth="1"/>
     <col min="6" max="6" width="15" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15" style="40" customWidth="1"/>
+    <col min="7" max="7" width="15" style="38" customWidth="1"/>
     <col min="8" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="14.75" customWidth="1"/>
     <col min="14" max="14" width="13.125" bestFit="1" customWidth="1"/>
@@ -6718,7 +6724,7 @@
       <c r="C9" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="35" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="23" t="s">
@@ -6727,13 +6733,13 @@
       <c r="F9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="39" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="14" t="s">
@@ -6758,28 +6764,28 @@
       <c r="A10" s="10">
         <v>1</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>46204</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="31">
         <v>249800.5</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <v>211385.5</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>773.5</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="31">
+      <c r="F10" s="31"/>
+      <c r="G10" s="30">
         <v>1644</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>210612</v>
       </c>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -6796,20 +6802,20 @@
       <c r="A11" s="10">
         <v>2</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="26">
         <v>46205</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="45"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="43"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -6826,28 +6832,28 @@
       <c r="A12" s="10">
         <v>3</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>46206</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="31">
         <v>272174.5</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="31">
         <v>231067</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="32">
+      <c r="E12" s="30"/>
+      <c r="F12" s="31">
         <v>517</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="30">
         <v>1308</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="31">
         <v>231584</v>
       </c>
-      <c r="I12" s="31"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -6864,20 +6870,20 @@
       <c r="A13" s="10">
         <v>4</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="26">
         <v>46207</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -6894,20 +6900,20 @@
       <c r="A14" s="10">
         <v>5</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="45"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -6924,28 +6930,28 @@
       <c r="A15" s="10">
         <v>6</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>46209</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="33">
         <v>255013.5</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <v>211456.5</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>765.5</v>
       </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31">
+      <c r="F15" s="30"/>
+      <c r="G15" s="30">
         <v>1950</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="33">
         <v>210691</v>
       </c>
-      <c r="I15" s="31"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="32"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="31"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
@@ -6962,28 +6968,28 @@
       <c r="A16" s="10">
         <v>7</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="26">
         <v>46210</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>325910</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <v>274485.5</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>1255.5</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31">
+      <c r="F16" s="30"/>
+      <c r="G16" s="30">
         <v>2496</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="33">
         <v>273230</v>
       </c>
-      <c r="I16" s="31"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="32"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -7000,28 +7006,28 @@
       <c r="A17" s="10">
         <v>8</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>46211</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>217925</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>185540</v>
       </c>
-      <c r="E17" s="31"/>
-      <c r="F17" s="34">
+      <c r="E17" s="30"/>
+      <c r="F17" s="33">
         <v>52</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="30">
         <v>1206</v>
       </c>
-      <c r="H17" s="34">
+      <c r="H17" s="33">
         <v>185592</v>
       </c>
-      <c r="I17" s="31"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="32"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -7038,28 +7044,28 @@
       <c r="A18" s="10">
         <v>9</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="26">
         <v>46212</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="31">
         <v>236707</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="31">
         <v>200869</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <v>204</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31">
+      <c r="F18" s="30"/>
+      <c r="G18" s="30">
         <v>1296</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="31">
         <v>200665</v>
       </c>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -7076,20 +7082,20 @@
       <c r="A19" s="10">
         <v>10</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="26">
         <v>46213</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="45"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="43"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -7106,20 +7112,20 @@
       <c r="A20" s="10">
         <v>11</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>46214</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="45"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="43"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -7136,20 +7142,20 @@
       <c r="A21" s="10">
         <v>12</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="45"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="43"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -7166,28 +7172,28 @@
       <c r="A22" s="10">
         <v>13</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="26">
         <v>46216</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="31">
         <v>264783</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="31">
         <v>223640.25</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="30">
         <v>149.25</v>
       </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="31">
+      <c r="F22" s="31"/>
+      <c r="G22" s="30">
         <v>1548</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="31">
         <v>223491</v>
       </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -7204,28 +7210,28 @@
       <c r="A23" s="10">
         <v>14</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="26">
         <v>46217</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="31">
         <v>2444360.33</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="31">
         <v>205234.33</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="30">
         <v>193.33</v>
       </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="31">
+      <c r="F23" s="31"/>
+      <c r="G23" s="30">
         <v>1296</v>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="31">
         <v>205041</v>
       </c>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="7"/>
@@ -7242,26 +7248,26 @@
       <c r="A24" s="10">
         <v>15</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="26">
         <v>46218</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="31">
         <v>151113.32999999999</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="31">
         <v>130290.33</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="30">
         <v>360.33</v>
       </c>
-      <c r="F24" s="34"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="34">
+      <c r="F24" s="33"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="33">
         <v>130290.33</v>
       </c>
-      <c r="I24" s="31"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="7"/>
@@ -7278,28 +7284,28 @@
       <c r="A25" s="10">
         <v>16</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="26">
         <v>46219</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="31">
         <v>278011.66666666669</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="31">
         <v>244719.16666666669</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="30">
         <v>84.17</v>
       </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31">
+      <c r="F25" s="30"/>
+      <c r="G25" s="30">
         <v>2004</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="31">
         <v>244635</v>
       </c>
-      <c r="I25" s="31"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="31"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="7"/>
@@ -7316,28 +7322,28 @@
       <c r="A26" s="10">
         <v>17</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>46220</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="31">
         <v>270113.33</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="31">
         <v>227409.83</v>
       </c>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32">
+      <c r="E26" s="30"/>
+      <c r="F26" s="31">
         <v>72.17</v>
       </c>
-      <c r="G26" s="31">
+      <c r="G26" s="30">
         <v>972</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="31">
         <v>227482</v>
       </c>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="17"/>
@@ -7354,20 +7360,20 @@
       <c r="A27" s="10">
         <v>18</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="26">
         <v>46221</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="45"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="43"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="7"/>
@@ -7384,20 +7390,20 @@
       <c r="A28" s="10">
         <v>19</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="45"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="43"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="7"/>
@@ -7414,28 +7420,28 @@
       <c r="A29" s="10">
         <v>20</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="26">
         <v>46223</v>
       </c>
       <c r="C29" s="11">
         <v>283390</v>
       </c>
-      <c r="D29" s="37">
+      <c r="D29" s="36">
         <v>238142.5</v>
       </c>
       <c r="E29" s="13">
         <v>721.5</v>
       </c>
       <c r="F29" s="11"/>
-      <c r="G29" s="42">
+      <c r="G29" s="40">
         <v>1776</v>
       </c>
-      <c r="H29" s="33">
+      <c r="H29" s="32">
         <v>237421</v>
       </c>
-      <c r="I29" s="42"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="30"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="29"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="7"/>
@@ -7452,28 +7458,28 @@
       <c r="A30" s="10">
         <v>21</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>46224</v>
       </c>
       <c r="C30" s="11">
         <v>151595</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="36">
         <v>124368.5</v>
       </c>
       <c r="E30" s="13">
         <v>234.5</v>
       </c>
       <c r="F30" s="11"/>
-      <c r="G30" s="42">
+      <c r="G30" s="40">
         <v>252</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="32">
         <v>124134</v>
       </c>
-      <c r="I30" s="42"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="30"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="29"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="7"/>
@@ -7490,28 +7496,28 @@
       <c r="A31" s="10">
         <v>22</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="26">
         <v>46225</v>
       </c>
       <c r="C31" s="11">
         <v>230482.54</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="36">
         <v>194682.04</v>
       </c>
       <c r="E31" s="13">
         <v>299.04000000000002</v>
       </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="42">
+      <c r="G31" s="40">
         <v>1668</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="32">
         <v>194383</v>
       </c>
-      <c r="I31" s="42"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="30"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="29"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="17"/>
@@ -7528,28 +7534,28 @@
       <c r="A32" s="10">
         <v>23</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>46226</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="31">
         <v>223968.88</v>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="31">
         <v>189405.13</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="30">
         <v>835.13</v>
       </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31">
+      <c r="F32" s="30"/>
+      <c r="G32" s="30">
         <v>1008</v>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="31">
         <v>188570</v>
       </c>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="7"/>
@@ -7566,28 +7572,28 @@
       <c r="A33" s="10">
         <v>24</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="26">
         <v>46227</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="31">
         <v>222577.58</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="31">
         <v>189464.33</v>
       </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="32">
+      <c r="E33" s="30"/>
+      <c r="F33" s="31">
         <v>631.66999999999996</v>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="30">
         <v>1380</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="31">
         <v>190096</v>
       </c>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="7"/>
@@ -7604,20 +7610,20 @@
       <c r="A34" s="10">
         <v>25</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>46228</v>
       </c>
-      <c r="C34" s="43" t="s">
+      <c r="C34" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="44"/>
-      <c r="K34" s="45"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="43"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="7"/>
@@ -7634,20 +7640,20 @@
       <c r="A35" s="10">
         <v>26</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C35" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="45"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="43"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="7"/>
@@ -7664,18 +7670,28 @@
       <c r="A36" s="10">
         <v>27</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="26">
         <v>46230</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="30"/>
+      <c r="C36" s="31">
+        <v>286690.33</v>
+      </c>
+      <c r="D36" s="31">
+        <v>241445.83</v>
+      </c>
+      <c r="E36" s="30">
+        <v>50.83</v>
+      </c>
+      <c r="F36" s="31"/>
+      <c r="G36" s="30">
+        <v>1596</v>
+      </c>
+      <c r="H36" s="31">
+        <v>241395</v>
+      </c>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="7"/>
@@ -7692,18 +7708,18 @@
       <c r="A37" s="10">
         <v>28</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="26">
         <v>46231</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="8"/>
@@ -7720,18 +7736,18 @@
       <c r="A38" s="10">
         <v>29</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="26">
         <v>46232</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="34"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="7"/>
@@ -7748,7 +7764,7 @@
       <c r="A39" s="10">
         <v>30</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="26">
         <v>46233</v>
       </c>
       <c r="C39" s="31"/>
@@ -7776,7 +7792,7 @@
       <c r="A40" s="10">
         <v>31</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="26">
         <v>46234</v>
       </c>
       <c r="C40" s="31"/>
@@ -7802,15 +7818,15 @@
     </row>
     <row r="41" spans="1:22" ht="15">
       <c r="A41" s="10"/>
-      <c r="B41" s="27"/>
+      <c r="B41" s="26"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
       <c r="K41" s="10"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -7826,16 +7842,16 @@
     </row>
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="21"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="43"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -7849,35 +7865,35 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="27"/>
+      <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6077926.1566666672</v>
+        <v>6364616.4866666673</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3282159.9066666667</v>
-      </c>
-      <c r="E43" s="28">
+        <v>3523605.7366666668</v>
+      </c>
+      <c r="E43" s="27">
         <f t="shared" si="0"/>
-        <v>5875.75</v>
+        <v>5926.58</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
         <v>1272.8399999999999</v>
       </c>
-      <c r="G43" s="28">
+      <c r="G43" s="27">
         <f t="shared" si="0"/>
-        <v>21804</v>
+        <v>23400</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3277917.33</v>
-      </c>
-      <c r="I43" s="28">
+        <v>3519312.33</v>
+      </c>
+      <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
         <v>0</v>
       </c>
@@ -7906,7 +7922,7 @@
       <c r="B44" s="1"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
-      <c r="E44" s="25"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
@@ -11914,7 +11930,7 @@
     <col min="3" max="4" width="14.875" customWidth="1"/>
     <col min="5" max="5" width="14.75" customWidth="1"/>
     <col min="6" max="6" width="15" style="15" customWidth="1"/>
-    <col min="7" max="7" width="15" style="40" customWidth="1"/>
+    <col min="7" max="7" width="15" style="38" customWidth="1"/>
     <col min="8" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="14.75" customWidth="1"/>
     <col min="14" max="14" width="13.125" bestFit="1" customWidth="1"/>
@@ -12081,7 +12097,7 @@
     </row>
     <row r="8" spans="1:22" ht="15">
       <c r="A8" s="5"/>
-      <c r="B8" s="38"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="1"/>
@@ -12113,7 +12129,7 @@
       <c r="C9" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="35" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="23" t="s">
@@ -12122,13 +12138,13 @@
       <c r="F9" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="39" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="39" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="14" t="s">
@@ -12153,28 +12169,28 @@
       <c r="A10" s="10">
         <v>1</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>46204</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="31">
         <v>297996.5</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <v>238892</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>21</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="31">
+      <c r="F10" s="31"/>
+      <c r="G10" s="30">
         <v>1350</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <v>238871</v>
       </c>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
@@ -12191,28 +12207,28 @@
       <c r="A11" s="10">
         <v>2</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="26">
         <v>46205</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="31">
         <v>253346.5</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="31">
         <v>213164</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32">
+      <c r="E11" s="30"/>
+      <c r="F11" s="31">
         <v>47</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="30">
         <v>1722</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="31">
         <v>213211</v>
       </c>
-      <c r="I11" s="31"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -12229,28 +12245,28 @@
       <c r="A12" s="10">
         <v>3</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="26">
         <v>46206</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="31">
         <v>438059</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="31">
         <v>402146.75</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="32">
+      <c r="E12" s="30"/>
+      <c r="F12" s="31">
         <v>67.25</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="30">
         <v>648</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="31">
         <v>402214</v>
       </c>
-      <c r="I12" s="31"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
@@ -12267,20 +12283,20 @@
       <c r="A13" s="10">
         <v>4</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="26">
         <v>46207</v>
       </c>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="45"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -12297,20 +12313,20 @@
       <c r="A14" s="10">
         <v>5</v>
       </c>
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="43" t="s">
+      <c r="C14" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="45"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
@@ -12327,28 +12343,28 @@
       <c r="A15" s="10">
         <v>6</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>46209</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="33">
         <v>299824</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="33">
         <v>247763.5</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>34.5</v>
       </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31">
+      <c r="F15" s="30"/>
+      <c r="G15" s="30">
         <v>2328</v>
       </c>
-      <c r="H15" s="34">
+      <c r="H15" s="33">
         <v>247729</v>
       </c>
-      <c r="I15" s="31"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="32">
+      <c r="I15" s="30"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="31">
         <v>50</v>
       </c>
       <c r="L15" s="1"/>
@@ -12367,28 +12383,28 @@
       <c r="A16" s="10">
         <v>7</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="26">
         <v>46210</v>
       </c>
-      <c r="C16" s="34">
+      <c r="C16" s="33">
         <v>287132</v>
       </c>
-      <c r="D16" s="34">
+      <c r="D16" s="33">
         <v>243548.75</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>2143.75</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31">
+      <c r="F16" s="30"/>
+      <c r="G16" s="30">
         <v>1824</v>
       </c>
-      <c r="H16" s="34">
+      <c r="H16" s="33">
         <v>241405</v>
       </c>
-      <c r="I16" s="31"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="32"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
@@ -12405,26 +12421,26 @@
       <c r="A17" s="10">
         <v>8</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>46211</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>349413</v>
       </c>
-      <c r="D17" s="34">
+      <c r="D17" s="33">
         <v>305021.5</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>2129.5</v>
       </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="34">
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="33">
         <v>302892</v>
       </c>
-      <c r="I17" s="31"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="32"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
@@ -12441,28 +12457,28 @@
       <c r="A18" s="10">
         <v>9</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="26">
         <v>46212</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="31">
         <v>112831.5</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="31">
         <v>94338</v>
       </c>
-      <c r="E18" s="31"/>
-      <c r="F18" s="32">
+      <c r="E18" s="30"/>
+      <c r="F18" s="31">
         <v>2094</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="30">
         <v>300</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="31">
         <v>96432</v>
       </c>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -12479,28 +12495,28 @@
       <c r="A19" s="10">
         <v>10</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="26">
         <v>46213</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="31">
         <v>249944.5</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="31">
         <v>211759.25</v>
       </c>
-      <c r="E19" s="31"/>
-      <c r="F19" s="34">
+      <c r="E19" s="30"/>
+      <c r="F19" s="33">
         <v>12.75</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="30">
         <v>942</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="33">
         <v>211772</v>
       </c>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -12517,20 +12533,20 @@
       <c r="A20" s="10">
         <v>11</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>46214</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="45"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="43"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -12547,20 +12563,20 @@
       <c r="A21" s="10">
         <v>12</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C21" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="44"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="45"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="43"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
@@ -12577,28 +12593,28 @@
       <c r="A22" s="10">
         <v>13</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="26">
         <v>46216</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="31">
         <v>386726.5</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="31">
         <v>322822.75</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="30">
         <v>3522.75</v>
       </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="31">
+      <c r="F22" s="31"/>
+      <c r="G22" s="30">
         <v>1296</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="31">
         <v>319300</v>
       </c>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
@@ -12615,28 +12631,28 @@
       <c r="A23" s="10">
         <v>14</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="26">
         <v>46217</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="31">
         <v>226895</v>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="31">
         <v>191038.5</v>
       </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32">
+      <c r="E23" s="31"/>
+      <c r="F23" s="31">
         <v>1106.5</v>
       </c>
-      <c r="G23" s="31">
+      <c r="G23" s="30">
         <v>1446</v>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="31">
         <v>192145</v>
       </c>
-      <c r="I23" s="32"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32">
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31">
         <v>50</v>
       </c>
       <c r="L23" s="1"/>
@@ -12655,28 +12671,28 @@
       <c r="A24" s="10">
         <v>15</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="26">
         <v>46218</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="31">
         <v>341541</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="31">
         <v>279441.75</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="30">
         <v>2872.75</v>
       </c>
-      <c r="F24" s="34"/>
-      <c r="G24" s="31">
+      <c r="F24" s="33"/>
+      <c r="G24" s="30">
         <v>1896</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="33">
         <v>276569</v>
       </c>
-      <c r="I24" s="31"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
       <c r="N24" s="7"/>
@@ -12693,28 +12709,28 @@
       <c r="A25" s="10">
         <v>16</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="26">
         <v>46219</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="31">
         <v>142129.5</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="31">
         <v>121441.5</v>
       </c>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32">
+      <c r="E25" s="30"/>
+      <c r="F25" s="31">
         <v>2442.5</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="30">
         <v>780</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="31">
         <v>123884</v>
       </c>
-      <c r="I25" s="31"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32">
+      <c r="I25" s="30"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31">
         <f>50+100</f>
         <v>150</v>
       </c>
@@ -12734,28 +12750,28 @@
       <c r="A26" s="10">
         <v>17</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>46220</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="31">
         <v>507045</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="31">
         <v>442359</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="30">
         <v>65</v>
       </c>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31">
+      <c r="F26" s="30"/>
+      <c r="G26" s="30">
         <v>2592</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="31">
         <v>442294</v>
       </c>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="17"/>
@@ -12772,20 +12788,20 @@
       <c r="A27" s="10">
         <v>18</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="26">
         <v>46221</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="45"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="43"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="N27" s="7"/>
@@ -12802,20 +12818,20 @@
       <c r="A28" s="10">
         <v>19</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C28" s="43" t="s">
+      <c r="C28" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="45"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="43"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="7"/>
@@ -12832,28 +12848,28 @@
       <c r="A29" s="10">
         <v>20</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="26">
         <v>46223</v>
       </c>
       <c r="C29" s="11">
         <v>510270</v>
       </c>
-      <c r="D29" s="37">
+      <c r="D29" s="36">
         <v>435177.25</v>
       </c>
       <c r="E29" s="13">
         <v>145.25</v>
       </c>
       <c r="F29" s="11"/>
-      <c r="G29" s="42">
+      <c r="G29" s="40">
         <v>1584</v>
       </c>
-      <c r="H29" s="33">
+      <c r="H29" s="32">
         <v>435032</v>
       </c>
-      <c r="I29" s="42"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="30">
+      <c r="I29" s="40"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="29">
         <v>50</v>
       </c>
       <c r="L29" s="1"/>
@@ -12872,28 +12888,28 @@
       <c r="A30" s="10">
         <v>21</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>46224</v>
       </c>
       <c r="C30" s="11">
         <v>344940</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="36">
         <v>262971.75</v>
       </c>
       <c r="E30" s="13">
         <v>104.75</v>
       </c>
       <c r="F30" s="11"/>
-      <c r="G30" s="42">
+      <c r="G30" s="40">
         <v>1104</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="32">
         <v>262867</v>
       </c>
-      <c r="I30" s="42"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="30">
+      <c r="I30" s="40"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="29">
         <v>24757.5</v>
       </c>
       <c r="L30" s="1"/>
@@ -12912,26 +12928,26 @@
       <c r="A31" s="10">
         <v>22</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="26">
         <v>46225</v>
       </c>
       <c r="C31" s="11">
         <v>408168</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="36">
         <v>371172.75</v>
       </c>
       <c r="E31" s="13">
         <v>0.75</v>
       </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="33">
+      <c r="G31" s="40"/>
+      <c r="H31" s="32">
         <v>371172</v>
       </c>
-      <c r="I31" s="42"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="30"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="29"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="17"/>
@@ -12948,28 +12964,28 @@
       <c r="A32" s="10">
         <v>23</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>46226</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="31">
         <v>407248</v>
       </c>
-      <c r="D32" s="32">
+      <c r="D32" s="31">
         <v>340907</v>
       </c>
-      <c r="E32" s="31"/>
-      <c r="F32" s="34">
+      <c r="E32" s="30"/>
+      <c r="F32" s="33">
         <v>52</v>
       </c>
-      <c r="G32" s="31">
+      <c r="G32" s="30">
         <v>1140</v>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="31">
         <v>340959</v>
       </c>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="34">
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="33">
         <v>50</v>
       </c>
       <c r="L32" s="1"/>
@@ -12988,28 +13004,28 @@
       <c r="A33" s="10">
         <v>24</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="26">
         <v>46227</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="31">
         <v>505296</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="31">
         <v>432331.5</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="30">
         <v>45.5</v>
       </c>
-      <c r="F33" s="32"/>
-      <c r="G33" s="31">
+      <c r="F33" s="31"/>
+      <c r="G33" s="30">
         <v>2946</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="31">
         <v>432286</v>
       </c>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="7"/>
@@ -13026,28 +13042,28 @@
       <c r="A34" s="10">
         <v>25</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>46228</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="31">
         <v>482911</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="31">
         <v>442009.75</v>
       </c>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32">
+      <c r="E34" s="31"/>
+      <c r="F34" s="31">
         <v>28.25</v>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="30">
         <v>1608</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="31">
         <v>442038</v>
       </c>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="7"/>
@@ -13064,20 +13080,20 @@
       <c r="A35" s="10">
         <v>26</v>
       </c>
-      <c r="B35" s="35" t="s">
+      <c r="B35" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C35" s="43" t="s">
+      <c r="C35" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="44"/>
-      <c r="J35" s="44"/>
-      <c r="K35" s="45"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="43"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="7"/>
@@ -13094,18 +13110,31 @@
       <c r="A36" s="10">
         <v>27</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="26">
         <v>46230</v>
       </c>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="30"/>
+      <c r="C36" s="31">
+        <v>243284.58</v>
+      </c>
+      <c r="D36" s="31">
+        <v>206638.33</v>
+      </c>
+      <c r="E36" s="30">
+        <v>48.33</v>
+      </c>
+      <c r="F36" s="31"/>
+      <c r="G36" s="30">
+        <f>1248</f>
+        <v>1248</v>
+      </c>
+      <c r="H36" s="31">
+        <v>206590</v>
+      </c>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31">
+        <v>50</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="7"/>
@@ -13122,18 +13151,18 @@
       <c r="A37" s="10">
         <v>28</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="26">
         <v>46231</v>
       </c>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="30"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="8"/>
@@ -13150,18 +13179,18 @@
       <c r="A38" s="10">
         <v>29</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="26">
         <v>46232</v>
       </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="39"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="34"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="7"/>
@@ -13178,7 +13207,7 @@
       <c r="A39" s="10">
         <v>30</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="26">
         <v>46233</v>
       </c>
       <c r="C39" s="31"/>
@@ -13206,7 +13235,7 @@
       <c r="A40" s="10">
         <v>31</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="26">
         <v>46234</v>
       </c>
       <c r="C40" s="31"/>
@@ -13232,15 +13261,15 @@
     </row>
     <row r="41" spans="1:22" ht="15">
       <c r="A41" s="10"/>
-      <c r="B41" s="27"/>
+      <c r="B41" s="26"/>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
       <c r="K41" s="10"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -13256,16 +13285,16 @@
     </row>
     <row r="42" spans="1:22" ht="15">
       <c r="A42" s="21"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="44"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="43"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="7"/>
@@ -13279,35 +13308,35 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15">
-      <c r="A43" s="26" t="s">
+      <c r="A43" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B43" s="27"/>
+      <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6551717</v>
+        <v>6795001.5800000001</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>5598307.25</v>
-      </c>
-      <c r="E43" s="28">
+        <v>5804945.5800000001</v>
+      </c>
+      <c r="E43" s="27">
         <f t="shared" si="0"/>
-        <v>11085.5</v>
+        <v>11133.83</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
         <v>5850.25</v>
       </c>
-      <c r="G43" s="28">
+      <c r="G43" s="27">
         <f t="shared" si="0"/>
-        <v>25506</v>
+        <v>26754</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>5593072</v>
-      </c>
-      <c r="I43" s="28">
+        <v>5799662</v>
+      </c>
+      <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
         <v>0</v>
       </c>
@@ -13317,7 +13346,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>25107.5</v>
+        <v>25157.5</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -13336,7 +13365,7 @@
       <c r="B44" s="1"/>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
-      <c r="E44" s="25"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="9"/>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F90EABD-27F6-4C9E-A862-CF54FCD644E6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E8BD8E-0E92-43AB-9E47-40E18094A748}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -293,6 +293,31 @@
           <t xml:space="preserve">
 SOUND CHECK
 SI NO. 11485</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I37" authorId="0" shapeId="0" xr:uid="{F16D790B-41EA-4372-8C67-922CC96E0EB8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+BALAMBAN STORE
+SI NO. 11493</t>
         </r>
       </text>
     </comment>
@@ -2307,13 +2332,25 @@
       <c r="B37" s="26">
         <v>46231</v>
       </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
+      <c r="C37" s="31">
+        <v>741172</v>
+      </c>
+      <c r="D37" s="31">
+        <v>663443.5</v>
+      </c>
+      <c r="E37" s="30">
+        <v>45.5</v>
+      </c>
       <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
+      <c r="G37" s="30">
+        <v>5064</v>
+      </c>
+      <c r="H37" s="31">
+        <v>663398</v>
+      </c>
+      <c r="I37" s="30">
+        <v>5850</v>
+      </c>
       <c r="J37" s="31"/>
       <c r="K37" s="31"/>
       <c r="L37" s="1"/>
@@ -2467,15 +2504,15 @@
       <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>5259341.5</v>
+        <v>6000513.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4114366.64</v>
+        <v>4777810.1400000006</v>
       </c>
       <c r="E43" s="27">
         <f t="shared" si="0"/>
-        <v>4310.0600000000004</v>
+        <v>4355.5600000000004</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -2483,15 +2520,15 @@
       </c>
       <c r="G43" s="27">
         <f t="shared" si="0"/>
-        <v>20694</v>
+        <v>25758</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>4359916</v>
+        <v>5023314</v>
       </c>
       <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>372029</v>
+        <v>377879</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -7711,12 +7748,20 @@
       <c r="B37" s="26">
         <v>46231</v>
       </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
+      <c r="C37" s="31">
+        <v>108235.67</v>
+      </c>
+      <c r="D37" s="31">
+        <v>91591.67</v>
+      </c>
+      <c r="E37" s="30">
+        <v>110.67</v>
+      </c>
       <c r="F37" s="31"/>
       <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
+      <c r="H37" s="31">
+        <v>91481</v>
+      </c>
       <c r="I37" s="31"/>
       <c r="J37" s="31"/>
       <c r="K37" s="31"/>
@@ -7871,15 +7916,15 @@
       <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6364616.4866666673</v>
+        <v>6472852.1566666672</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3523605.7366666668</v>
+        <v>3615197.4066666667</v>
       </c>
       <c r="E43" s="27">
         <f t="shared" si="0"/>
-        <v>5926.58</v>
+        <v>6037.25</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -7891,7 +7936,7 @@
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3519312.33</v>
+        <v>3610793.33</v>
       </c>
       <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13154,12 +13199,22 @@
       <c r="B37" s="26">
         <v>46231</v>
       </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
+      <c r="C37" s="31">
+        <v>230936.25</v>
+      </c>
+      <c r="D37" s="31">
+        <v>194547.75</v>
+      </c>
       <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
+      <c r="F37" s="31">
+        <v>773.25</v>
+      </c>
+      <c r="G37" s="30">
+        <v>1812</v>
+      </c>
+      <c r="H37" s="31">
+        <v>195321</v>
+      </c>
       <c r="I37" s="31"/>
       <c r="J37" s="31"/>
       <c r="K37" s="31"/>
@@ -13314,11 +13369,11 @@
       <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6795001.5800000001</v>
+        <v>7025937.8300000001</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>5804945.5800000001</v>
+        <v>5999493.3300000001</v>
       </c>
       <c r="E43" s="27">
         <f t="shared" si="0"/>
@@ -13326,15 +13381,15 @@
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>5850.25</v>
+        <v>6623.5</v>
       </c>
       <c r="G43" s="27">
         <f t="shared" si="0"/>
-        <v>26754</v>
+        <v>28566</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>5799662</v>
+        <v>5994983</v>
       </c>
       <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E8BD8E-0E92-43AB-9E47-40E18094A748}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECA5BA6-1C0B-4F6F-A629-D62D9D116090}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
   <sheets>
     <sheet name="JULY, SRS R1" sheetId="6" r:id="rId1"/>
@@ -179,7 +179,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -188,7 +188,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 BALWARTE
@@ -204,7 +204,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -213,7 +213,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 BALWARTE
@@ -254,7 +254,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -263,7 +263,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 SOUND CHECK
@@ -279,7 +279,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -288,7 +288,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 SOUND CHECK
@@ -297,6 +297,57 @@
       </text>
     </comment>
     <comment ref="I37" authorId="0" shapeId="0" xr:uid="{F16D790B-41EA-4372-8C67-922CC96E0EB8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+BALAMBAN STORE
+SI NO. 11493</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{71DCCC3B-9A4A-46AC-BBF5-DC48C94B5918}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DANYEN STORE
+SI NO. 11497
+PROMO</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J39" authorId="0" shapeId="0" xr:uid="{164CCB24-F2B7-4FB4-816C-A97C897AD79F}">
       <text>
         <r>
           <rPr>
@@ -331,6 +382,41 @@
     <author>User</author>
   </authors>
   <commentList>
+    <comment ref="I38" authorId="0" shapeId="0" xr:uid="{32E1AEDB-911A-463F-A38D-988F41BF28D7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SOUND CHECK
+SI NO. 11623</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
     <comment ref="K30" authorId="0" shapeId="0" xr:uid="{A4516D3E-FA50-4CA0-9404-5EB8FC48E51A}">
       <text>
         <r>
@@ -339,7 +425,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -348,7 +434,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 INCENTIVES HENSON</t>
@@ -475,7 +561,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -587,19 +673,6 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2372,13 +2445,25 @@
       <c r="B38" s="26">
         <v>46232</v>
       </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
+      <c r="C38" s="31">
+        <v>820688</v>
+      </c>
+      <c r="D38" s="31">
+        <v>744975</v>
+      </c>
       <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
+      <c r="F38" s="31">
+        <v>37</v>
+      </c>
+      <c r="G38" s="30">
+        <v>6012</v>
+      </c>
+      <c r="H38" s="31">
+        <v>775012</v>
+      </c>
+      <c r="I38" s="30">
+        <v>10400</v>
+      </c>
       <c r="J38" s="31"/>
       <c r="K38" s="31"/>
       <c r="L38" s="1"/>
@@ -2400,15 +2485,28 @@
       <c r="B39" s="26">
         <v>46233</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
+      <c r="C39" s="31">
+        <v>270506</v>
+      </c>
+      <c r="D39" s="31">
+        <v>245642.75</v>
+      </c>
+      <c r="E39" s="30">
+        <v>5.75</v>
+      </c>
       <c r="F39" s="31"/>
       <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
+      <c r="H39" s="31">
+        <v>245637</v>
+      </c>
       <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
+      <c r="J39" s="30">
+        <v>5850</v>
+      </c>
+      <c r="K39" s="31">
+        <f>3900+5850</f>
+        <v>9750</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="7"/>
@@ -2504,39 +2602,39 @@
       <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6000513.5</v>
+        <v>7091707.5</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>4777810.1400000006</v>
+        <v>5768427.8900000006</v>
       </c>
       <c r="E43" s="27">
         <f t="shared" si="0"/>
-        <v>4355.5600000000004</v>
+        <v>4361.3100000000004</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>5468.85</v>
+        <v>5505.85</v>
       </c>
       <c r="G43" s="27">
         <f t="shared" si="0"/>
-        <v>25758</v>
+        <v>31770</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>5023314</v>
+        <v>6043963</v>
       </c>
       <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>377879</v>
+        <v>388279</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>281270</v>
+        <v>287120</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>220.54000000000002</v>
+        <v>9970.5400000000009</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -6553,7 +6651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E574FF03-14F0-421D-8F76-5519CF1A2460}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E574FF03-14F0-421D-8F76-5519CF1A2460}">
   <dimension ref="A1:V279"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -7784,13 +7882,25 @@
       <c r="B38" s="26">
         <v>46232</v>
       </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
+      <c r="C38" s="31">
+        <v>245027.13</v>
+      </c>
+      <c r="D38" s="31">
+        <v>134194.13</v>
+      </c>
       <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
+      <c r="F38" s="31">
+        <v>1034.8800000000001</v>
+      </c>
+      <c r="G38" s="30">
+        <v>732</v>
+      </c>
+      <c r="H38" s="31">
+        <v>135229</v>
+      </c>
+      <c r="I38" s="31">
+        <v>69862</v>
+      </c>
       <c r="J38" s="31"/>
       <c r="K38" s="31"/>
       <c r="L38" s="1"/>
@@ -7812,12 +7922,22 @@
       <c r="B39" s="26">
         <v>46233</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
+      <c r="C39" s="31">
+        <v>217752.88</v>
+      </c>
+      <c r="D39" s="31">
+        <v>184352.38</v>
+      </c>
+      <c r="E39" s="30">
+        <v>29.38</v>
+      </c>
       <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
+      <c r="G39" s="30">
+        <v>1296</v>
+      </c>
+      <c r="H39" s="31">
+        <v>184323</v>
+      </c>
       <c r="I39" s="31"/>
       <c r="J39" s="31"/>
       <c r="K39" s="31"/>
@@ -7916,31 +8036,31 @@
       <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>6472852.1566666672</v>
+        <v>6935632.166666667</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>3615197.4066666667</v>
+        <v>3933743.9166666665</v>
       </c>
       <c r="E43" s="27">
         <f t="shared" si="0"/>
-        <v>6037.25</v>
+        <v>6066.63</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
-        <v>1272.8399999999999</v>
+        <v>2307.7200000000003</v>
       </c>
       <c r="G43" s="27">
         <f t="shared" si="0"/>
-        <v>23400</v>
+        <v>25428</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>3610793.33</v>
+        <v>3930345.33</v>
       </c>
       <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>0</v>
+        <v>69862</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
@@ -11962,6 +12082,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="99" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -13237,12 +13358,22 @@
       <c r="B38" s="26">
         <v>46232</v>
       </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
+      <c r="C38" s="31">
+        <v>426347.04</v>
+      </c>
+      <c r="D38" s="31">
+        <v>362142.54</v>
+      </c>
+      <c r="E38" s="30">
+        <v>630.54</v>
+      </c>
       <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
+      <c r="G38" s="30">
+        <v>1260</v>
+      </c>
+      <c r="H38" s="31">
+        <v>361512</v>
+      </c>
       <c r="I38" s="31"/>
       <c r="J38" s="31"/>
       <c r="K38" s="31"/>
@@ -13265,15 +13396,28 @@
       <c r="B39" s="26">
         <v>46233</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
+      <c r="C39" s="31">
+        <v>221615.71</v>
+      </c>
+      <c r="D39" s="31">
+        <v>188533.46</v>
+      </c>
+      <c r="E39" s="30">
+        <v>71.459999999999994</v>
+      </c>
       <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
+      <c r="G39" s="30">
+        <v>792</v>
+      </c>
+      <c r="H39" s="31">
+        <f>188462</f>
+        <v>188462</v>
+      </c>
       <c r="I39" s="31"/>
       <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
+      <c r="K39" s="31">
+        <v>50</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="7"/>
@@ -13369,15 +13513,15 @@
       <c r="B43" s="26"/>
       <c r="C43" s="16">
         <f t="shared" ref="C43:H43" si="0">SUM(C10:C42)</f>
-        <v>7025937.8300000001</v>
+        <v>7673900.5800000001</v>
       </c>
       <c r="D43" s="16">
         <f t="shared" si="0"/>
-        <v>5999493.3300000001</v>
+        <v>6550169.3300000001</v>
       </c>
       <c r="E43" s="27">
         <f t="shared" si="0"/>
-        <v>11133.83</v>
+        <v>11835.829999999998</v>
       </c>
       <c r="F43" s="16">
         <f t="shared" si="0"/>
@@ -13385,11 +13529,11 @@
       </c>
       <c r="G43" s="27">
         <f t="shared" si="0"/>
-        <v>28566</v>
+        <v>30618</v>
       </c>
       <c r="H43" s="16">
         <f t="shared" si="0"/>
-        <v>5994983</v>
+        <v>6544957</v>
       </c>
       <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
@@ -13401,7 +13545,7 @@
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>25157.5</v>
+        <v>25207.5</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>

--- a/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/SHORT OVER ALL ROUTES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECA5BA6-1C0B-4F6F-A629-D62D9D116090}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C80596E-58E8-4CE4-937C-5382DEF80A86}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{B997F013-12E6-4AA2-8A9D-EFCC32EA76C2}"/>
   </bookViews>
@@ -347,7 +347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J39" authorId="0" shapeId="0" xr:uid="{164CCB24-F2B7-4FB4-816C-A97C897AD79F}">
+    <comment ref="I39" authorId="0" shapeId="0" xr:uid="{60021DD0-DC88-4C70-B621-E861E7DA46F5}">
       <text>
         <r>
           <rPr>
@@ -355,7 +355,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t>User:</t>
         </r>
@@ -364,11 +364,11 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-BALAMBAN STORE
-SI NO. 11493</t>
+PIZON MINIMART
+SI NO. 11499</t>
         </r>
       </text>
     </comment>
@@ -561,7 +561,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -673,6 +673,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2499,14 +2512,11 @@
       <c r="H39" s="31">
         <v>245637</v>
       </c>
-      <c r="I39" s="31"/>
-      <c r="J39" s="30">
-        <v>5850</v>
-      </c>
-      <c r="K39" s="31">
-        <f>3900+5850</f>
-        <v>9750</v>
-      </c>
+      <c r="I39" s="30">
+        <v>3900</v>
+      </c>
+      <c r="J39" s="30"/>
+      <c r="K39" s="31"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="7"/>
@@ -2626,15 +2636,15 @@
       </c>
       <c r="I43" s="27">
         <f t="shared" ref="I43:J43" si="1">SUM(I10:I42)</f>
-        <v>388279</v>
+        <v>392179</v>
       </c>
       <c r="J43" s="16">
         <f t="shared" si="1"/>
-        <v>287120</v>
+        <v>281270</v>
       </c>
       <c r="K43" s="16">
         <f>SUM(K10:K42)</f>
-        <v>9970.5400000000009</v>
+        <v>220.54000000000002</v>
       </c>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
